--- a/data/GPS-Daten_Knotenpunkte_komplett.xlsx
+++ b/data/GPS-Daten_Knotenpunkte_komplett.xlsx
@@ -1,25 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://trsev.sharepoint.com/sites/BSP/Freigegebene Dokumente/BAR/Kompetenzfelder/Radtourismus/01 gesamtes Knotenpunktnetz BSP/Knotenpunkte/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu\home\pwahs\mdzt\route-picker\example\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1383" documentId="13_ncr:1_{BD092A85-E653-4418-9CFB-44635BC515DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F5500740-7BD3-46CC-B2AD-25C00561D67F}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A82189EE-1E41-4110-98DA-66FB5718C1A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{23F1768A-3F72-45A9-BD77-FBDC69BB0BBF}"/>
+    <workbookView xWindow="48015" yWindow="5385" windowWidth="17505" windowHeight="10485" firstSheet="1" activeTab="1" xr2:uid="{23F1768A-3F72-45A9-BD77-FBDC69BB0BBF}"/>
   </bookViews>
   <sheets>
     <sheet name="ehem. BARnimer Land" sheetId="1" r:id="rId1"/>
-    <sheet name="ehem. Ruppiner Seenland" sheetId="4" r:id="rId2"/>
+    <sheet name="Knotenpunkt" sheetId="4" r:id="rId2"/>
     <sheet name="Nachbarregionen" sheetId="2" r:id="rId3"/>
-    <sheet name="geplante Knotenpunkte" sheetId="3" r:id="rId4"/>
+    <sheet name="Knotenpunkt in Planung" sheetId="3" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'geplante Knotenpunkte'!$A$2:$C$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Knotenpunkt in Planung'!$A$2:$C$19</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -2051,12 +2051,6 @@
     <t>13.3387316°E</t>
   </si>
   <si>
-    <t>52.74467°N</t>
-  </si>
-  <si>
-    <t>13.255641°E</t>
-  </si>
-  <si>
     <t>52.9329251°N</t>
   </si>
   <si>
@@ -2076,13 +2070,19 @@
   </si>
   <si>
     <t>Knotenpunkte außerhalb der Brandenburgischen Seenplatte --&gt; bitte als graue Kreise  mit Zahlen markieren</t>
+  </si>
+  <si>
+    <t>52.7451807°N</t>
+  </si>
+  <si>
+    <t>13.2556527°E</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="14"/>
       <color theme="1"/>
@@ -2111,6 +2111,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri Light"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -2243,7 +2249,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2266,51 +2272,32 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Standard" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2353,8 +2340,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="5044440" y="662940"/>
-          <a:ext cx="510540" cy="487680"/>
+          <a:off x="4913630" y="678815"/>
+          <a:ext cx="503555" cy="522605"/>
           <a:chOff x="4792980" y="594360"/>
           <a:chExt cx="510540" cy="487680"/>
         </a:xfrm>
@@ -2500,8 +2487,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="6774180" y="556260"/>
-          <a:ext cx="510540" cy="487680"/>
+          <a:off x="6697345" y="578485"/>
+          <a:ext cx="494030" cy="500380"/>
           <a:chOff x="4792980" y="594360"/>
           <a:chExt cx="510540" cy="487680"/>
         </a:xfrm>
@@ -2647,8 +2634,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="4876800" y="685800"/>
-          <a:ext cx="510540" cy="487680"/>
+          <a:off x="4810125" y="714375"/>
+          <a:ext cx="507365" cy="503555"/>
           <a:chOff x="4792980" y="594360"/>
           <a:chExt cx="510540" cy="487680"/>
         </a:xfrm>
@@ -2796,8 +2783,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="6903720" y="533400"/>
-          <a:ext cx="510540" cy="487680"/>
+          <a:off x="6810375" y="552450"/>
+          <a:ext cx="507365" cy="494030"/>
           <a:chOff x="4800600" y="594360"/>
           <a:chExt cx="510540" cy="487680"/>
         </a:xfrm>
@@ -2921,9 +2908,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 – 2022-Design">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 – 2022">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2961,7 +2948,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 – 2022">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -3067,7 +3054,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 – 2022">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -3217,16 +3204,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E97CD67-8FAA-47FC-9A22-4853ED3C82A5}">
-  <dimension ref="A1:I104"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="18" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:I72"/>
+  <sheetFormatPr defaultColWidth="10.85546875" defaultRowHeight="18.5" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="11.75" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.1640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.83203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.85546875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A1" s="5" t="s">
         <v>268</v>
       </c>
@@ -3239,1238 +3226,17 @@
       <c r="H1" s="3"/>
       <c r="I1" s="3"/>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A2" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="B2" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="10"/>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A3" s="11">
-        <v>1</v>
-      </c>
-      <c r="B3" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="13" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3" s="13"/>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A4" s="11">
-        <v>2</v>
-      </c>
-      <c r="B4" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="C4" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="D4" s="13"/>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A5" s="11">
-        <v>3</v>
-      </c>
-      <c r="B5" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="C5" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="D5" s="13"/>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A6" s="11">
-        <v>4</v>
-      </c>
-      <c r="B6" s="13" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" s="13" t="s">
-        <v>8</v>
-      </c>
-      <c r="D6" s="13"/>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A7" s="11">
-        <v>5</v>
-      </c>
-      <c r="B7" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="D7" s="13"/>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A8" s="11">
-        <v>6</v>
-      </c>
-      <c r="B8" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="C8" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="D8" s="13"/>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A9" s="11">
-        <v>7</v>
-      </c>
-      <c r="B9" s="13" t="s">
-        <v>13</v>
-      </c>
-      <c r="C9" s="13" t="s">
-        <v>14</v>
-      </c>
-      <c r="D9" s="13"/>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A10" s="11">
-        <v>8</v>
-      </c>
-      <c r="B10" s="13" t="s">
-        <v>15</v>
-      </c>
-      <c r="C10" s="13" t="s">
-        <v>16</v>
-      </c>
-      <c r="D10" s="13"/>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A11" s="11">
-        <v>9</v>
-      </c>
-      <c r="B11" s="13" t="s">
-        <v>17</v>
-      </c>
-      <c r="C11" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="D11" s="13"/>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A12" s="11">
-        <v>10</v>
-      </c>
-      <c r="B12" s="13" t="s">
-        <v>19</v>
-      </c>
-      <c r="C12" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D12" s="13"/>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A13" s="11">
-        <v>11</v>
-      </c>
-      <c r="B13" s="13" t="s">
-        <v>241</v>
-      </c>
-      <c r="C13" s="13" t="s">
-        <v>240</v>
-      </c>
-      <c r="D13" s="13"/>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A14" s="11">
-        <v>12</v>
-      </c>
-      <c r="B14" s="13" t="s">
-        <v>239</v>
-      </c>
-      <c r="C14" s="13" t="s">
-        <v>238</v>
-      </c>
-      <c r="D14" s="13"/>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A15" s="11">
-        <v>13</v>
-      </c>
-      <c r="B15" s="13" t="s">
-        <v>255</v>
-      </c>
-      <c r="C15" s="13" t="s">
-        <v>254</v>
-      </c>
-      <c r="D15" s="13"/>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A16" s="11">
-        <v>14</v>
-      </c>
-      <c r="B16" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="C16" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="D16" s="13"/>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A17" s="11">
-        <v>15</v>
-      </c>
-      <c r="B17" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="C17" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="D17" s="13"/>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A18" s="11">
-        <v>16</v>
-      </c>
-      <c r="B18" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="C18" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="D18" s="13"/>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A19" s="11">
-        <v>17</v>
-      </c>
-      <c r="B19" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="C19" s="13" t="s">
-        <v>28</v>
-      </c>
-      <c r="D19" s="13"/>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A20" s="11">
-        <v>18</v>
-      </c>
-      <c r="B20" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="C20" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="D20" s="13"/>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A21" s="11">
-        <v>19</v>
-      </c>
-      <c r="B21" s="13" t="s">
-        <v>245</v>
-      </c>
-      <c r="C21" s="13" t="s">
-        <v>244</v>
-      </c>
-      <c r="D21" s="13"/>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A22" s="11">
-        <v>20</v>
-      </c>
-      <c r="B22" s="13" t="s">
-        <v>243</v>
-      </c>
-      <c r="C22" s="13" t="s">
-        <v>242</v>
-      </c>
-      <c r="D22" s="13"/>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A23" s="11">
-        <v>21</v>
-      </c>
-      <c r="B23" s="13" t="s">
-        <v>257</v>
-      </c>
-      <c r="C23" s="13" t="s">
-        <v>256</v>
-      </c>
-      <c r="D23" s="13"/>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A24" s="11">
-        <v>22</v>
-      </c>
-      <c r="B24" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="C24" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="D24" s="13"/>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A25" s="11">
-        <v>23</v>
-      </c>
-      <c r="B25" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="C25" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="D25" s="13"/>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A26" s="11">
-        <v>24</v>
-      </c>
-      <c r="B26" s="13" t="s">
-        <v>259</v>
-      </c>
-      <c r="C26" s="13" t="s">
-        <v>258</v>
-      </c>
-      <c r="D26" s="13"/>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A27" s="11">
-        <v>25</v>
-      </c>
-      <c r="B27" s="13" t="s">
-        <v>246</v>
-      </c>
-      <c r="C27" s="13" t="s">
-        <v>247</v>
-      </c>
-      <c r="D27" s="13"/>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A28" s="11">
-        <v>26</v>
-      </c>
-      <c r="B28" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="C28" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="D28" s="13"/>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A29" s="11">
-        <v>27</v>
-      </c>
-      <c r="B29" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="C29" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="D29" s="13"/>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A30" s="11">
-        <v>28</v>
-      </c>
-      <c r="B30" s="13" t="s">
-        <v>40</v>
-      </c>
-      <c r="C30" s="13" t="s">
-        <v>41</v>
-      </c>
-      <c r="D30" s="13"/>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A31" s="11">
-        <v>29</v>
-      </c>
-      <c r="B31" s="13" t="s">
-        <v>42</v>
-      </c>
-      <c r="C31" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="D31" s="13"/>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A32" s="11">
-        <v>30</v>
-      </c>
-      <c r="B32" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="C32" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="D32" s="13"/>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A33" s="11">
-        <v>31</v>
-      </c>
-      <c r="B33" s="13" t="s">
-        <v>261</v>
-      </c>
-      <c r="C33" s="13" t="s">
-        <v>260</v>
-      </c>
-      <c r="D33" s="13"/>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A34" s="11">
-        <v>32</v>
-      </c>
-      <c r="B34" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="C34" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="D34" s="13"/>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A35" s="11">
-        <v>33</v>
-      </c>
-      <c r="B35" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="C35" s="13" t="s">
-        <v>49</v>
-      </c>
-      <c r="D35" s="13"/>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A36" s="11">
-        <v>34</v>
-      </c>
-      <c r="B36" s="13" t="s">
-        <v>50</v>
-      </c>
-      <c r="C36" s="13" t="s">
-        <v>51</v>
-      </c>
-      <c r="D36" s="13"/>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A37" s="11">
-        <v>35</v>
-      </c>
-      <c r="B37" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="C37" s="13" t="s">
-        <v>53</v>
-      </c>
-      <c r="D37" s="13"/>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A38" s="11">
-        <v>36</v>
-      </c>
-      <c r="B38" s="13" t="s">
-        <v>253</v>
-      </c>
-      <c r="C38" s="13" t="s">
-        <v>252</v>
-      </c>
-      <c r="D38" s="13"/>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A39" s="11">
-        <v>37</v>
-      </c>
-      <c r="B39" s="13" t="s">
-        <v>54</v>
-      </c>
-      <c r="C39" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="D39" s="13"/>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A40" s="11">
-        <v>38</v>
-      </c>
-      <c r="B40" s="13" t="s">
-        <v>56</v>
-      </c>
-      <c r="C40" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="D40" s="13"/>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A41" s="11">
-        <v>39</v>
-      </c>
-      <c r="B41" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="C41" s="13" t="s">
-        <v>59</v>
-      </c>
-      <c r="D41" s="13"/>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A42" s="11">
-        <v>40</v>
-      </c>
-      <c r="B42" s="13" t="s">
-        <v>60</v>
-      </c>
-      <c r="C42" s="13" t="s">
-        <v>61</v>
-      </c>
-      <c r="D42" s="13"/>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A43" s="11">
-        <v>41</v>
-      </c>
-      <c r="B43" s="13" t="s">
-        <v>62</v>
-      </c>
-      <c r="C43" s="13" t="s">
-        <v>63</v>
-      </c>
-      <c r="D43" s="13"/>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A44" s="11">
-        <v>41</v>
-      </c>
-      <c r="B44" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="C44" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="D44" s="13"/>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A45" s="11">
-        <v>42</v>
-      </c>
-      <c r="B45" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="C45" s="13" t="s">
-        <v>67</v>
-      </c>
-      <c r="D45" s="13"/>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A46" s="11">
-        <v>43</v>
-      </c>
-      <c r="B46" s="13" t="s">
-        <v>68</v>
-      </c>
-      <c r="C46" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="D46" s="13"/>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A47" s="11">
-        <v>44</v>
-      </c>
-      <c r="B47" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="C47" s="13" t="s">
-        <v>71</v>
-      </c>
-      <c r="D47" s="13"/>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A48" s="11">
-        <v>45</v>
-      </c>
-      <c r="B48" s="13" t="s">
-        <v>263</v>
-      </c>
-      <c r="C48" s="13" t="s">
-        <v>262</v>
-      </c>
-      <c r="D48" s="13"/>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A49" s="11">
-        <v>46</v>
-      </c>
-      <c r="B49" s="13" t="s">
-        <v>265</v>
-      </c>
-      <c r="C49" s="13" t="s">
-        <v>264</v>
-      </c>
-      <c r="D49" s="13"/>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A50" s="11">
-        <v>47</v>
-      </c>
-      <c r="B50" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="C50" s="13" t="s">
-        <v>73</v>
-      </c>
-      <c r="D50" s="13"/>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A51" s="11">
-        <v>48</v>
-      </c>
-      <c r="B51" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="C51" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="D51" s="13"/>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A52" s="11">
-        <v>49</v>
-      </c>
-      <c r="B52" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="C52" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="D52" s="13"/>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A53" s="11">
-        <v>50</v>
-      </c>
-      <c r="B53" s="13" t="s">
-        <v>78</v>
-      </c>
-      <c r="C53" s="13" t="s">
-        <v>79</v>
-      </c>
-      <c r="D53" s="13"/>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A54" s="11">
-        <v>51</v>
-      </c>
-      <c r="B54" s="13" t="s">
-        <v>80</v>
-      </c>
-      <c r="C54" s="13" t="s">
-        <v>81</v>
-      </c>
-      <c r="D54" s="13"/>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A55" s="11">
-        <v>52</v>
-      </c>
-      <c r="B55" s="13" t="s">
-        <v>235</v>
-      </c>
-      <c r="C55" s="13" t="s">
-        <v>234</v>
-      </c>
-      <c r="D55" s="13"/>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A56" s="11">
-        <v>52</v>
-      </c>
-      <c r="B56" s="13" t="s">
-        <v>82</v>
-      </c>
-      <c r="C56" s="13" t="s">
-        <v>83</v>
-      </c>
-      <c r="D56" s="13"/>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A57" s="11">
-        <v>53</v>
-      </c>
-      <c r="B57" s="13" t="s">
-        <v>84</v>
-      </c>
-      <c r="C57" s="13" t="s">
-        <v>85</v>
-      </c>
-      <c r="D57" s="13"/>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A58" s="11">
-        <v>53</v>
-      </c>
-      <c r="B58" s="13" t="s">
-        <v>86</v>
-      </c>
-      <c r="C58" s="13" t="s">
-        <v>87</v>
-      </c>
-      <c r="D58" s="13"/>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A59" s="11">
-        <v>54</v>
-      </c>
-      <c r="B59" s="13" t="s">
-        <v>88</v>
-      </c>
-      <c r="C59" s="13" t="s">
-        <v>89</v>
-      </c>
-      <c r="D59" s="13"/>
-    </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A60" s="11">
-        <v>55</v>
-      </c>
-      <c r="B60" s="13" t="s">
-        <v>90</v>
-      </c>
-      <c r="C60" s="13" t="s">
-        <v>91</v>
-      </c>
-      <c r="D60" s="13"/>
-    </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A61" s="11">
-        <v>56</v>
-      </c>
-      <c r="B61" s="13" t="s">
-        <v>92</v>
-      </c>
-      <c r="C61" s="13" t="s">
-        <v>93</v>
-      </c>
-      <c r="D61" s="13"/>
-    </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A62" s="11">
-        <v>57</v>
-      </c>
-      <c r="B62" s="13" t="s">
-        <v>94</v>
-      </c>
-      <c r="C62" s="13" t="s">
-        <v>95</v>
-      </c>
-      <c r="D62" s="13"/>
-    </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A63" s="11">
-        <v>58</v>
-      </c>
-      <c r="B63" s="13" t="s">
-        <v>96</v>
-      </c>
-      <c r="C63" s="13" t="s">
-        <v>97</v>
-      </c>
-      <c r="D63" s="13"/>
-    </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A64" s="11">
-        <v>59</v>
-      </c>
-      <c r="B64" s="13" t="s">
-        <v>98</v>
-      </c>
-      <c r="C64" s="13" t="s">
-        <v>99</v>
-      </c>
-      <c r="D64" s="13"/>
-    </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A65" s="11">
-        <v>60</v>
-      </c>
-      <c r="B65" s="13" t="s">
-        <v>100</v>
-      </c>
-      <c r="C65" s="13" t="s">
-        <v>101</v>
-      </c>
-      <c r="D65" s="13"/>
-    </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A66" s="11">
-        <v>61</v>
-      </c>
-      <c r="B66" s="13" t="s">
-        <v>102</v>
-      </c>
-      <c r="C66" s="13" t="s">
-        <v>103</v>
-      </c>
-      <c r="D66" s="13"/>
-    </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A67" s="11">
-        <v>62</v>
-      </c>
-      <c r="B67" s="13" t="s">
-        <v>104</v>
-      </c>
-      <c r="C67" s="13" t="s">
-        <v>105</v>
-      </c>
-      <c r="D67" s="13"/>
-    </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A68" s="11">
-        <v>63</v>
-      </c>
-      <c r="B68" s="13" t="s">
-        <v>106</v>
-      </c>
-      <c r="C68" s="13" t="s">
-        <v>107</v>
-      </c>
-      <c r="D68" s="13"/>
-    </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A69" s="11">
-        <v>64</v>
-      </c>
-      <c r="B69" s="13" t="s">
-        <v>108</v>
-      </c>
-      <c r="C69" s="13" t="s">
-        <v>109</v>
-      </c>
-      <c r="D69" s="13"/>
-    </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A70" s="11">
-        <v>65</v>
-      </c>
-      <c r="B70" s="13" t="s">
-        <v>110</v>
-      </c>
-      <c r="C70" s="13" t="s">
-        <v>111</v>
-      </c>
-      <c r="D70" s="13"/>
-    </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A71" s="11">
-        <v>66</v>
-      </c>
-      <c r="B71" s="13" t="s">
-        <v>112</v>
-      </c>
-      <c r="C71" s="13" t="s">
-        <v>113</v>
-      </c>
-      <c r="D71" s="13"/>
-    </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A72" s="11">
-        <v>67</v>
-      </c>
-      <c r="B72" s="13" t="s">
-        <v>267</v>
-      </c>
-      <c r="C72" s="13" t="s">
-        <v>266</v>
-      </c>
+      <c r="C2" s="19"/>
+    </row>
+    <row r="72" spans="4:4" x14ac:dyDescent="0.45">
       <c r="D72" s="2"/>
-    </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A73" s="11">
-        <v>68</v>
-      </c>
-      <c r="B73" s="13" t="s">
-        <v>114</v>
-      </c>
-      <c r="C73" s="13" t="s">
-        <v>115</v>
-      </c>
-      <c r="D73" s="13"/>
-    </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A74" s="11">
-        <v>69</v>
-      </c>
-      <c r="B74" s="13" t="s">
-        <v>116</v>
-      </c>
-      <c r="C74" s="13" t="s">
-        <v>117</v>
-      </c>
-      <c r="D74" s="13"/>
-    </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A75" s="11">
-        <v>70</v>
-      </c>
-      <c r="B75" s="13" t="s">
-        <v>118</v>
-      </c>
-      <c r="C75" s="13" t="s">
-        <v>119</v>
-      </c>
-      <c r="D75" s="13"/>
-    </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A76" s="11">
-        <v>71</v>
-      </c>
-      <c r="B76" s="13" t="s">
-        <v>120</v>
-      </c>
-      <c r="C76" s="13" t="s">
-        <v>121</v>
-      </c>
-      <c r="D76" s="13"/>
-    </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A77" s="11">
-        <v>72</v>
-      </c>
-      <c r="B77" s="13" t="s">
-        <v>122</v>
-      </c>
-      <c r="C77" s="13" t="s">
-        <v>123</v>
-      </c>
-      <c r="D77" s="13"/>
-    </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A78" s="11">
-        <v>73</v>
-      </c>
-      <c r="B78" s="13" t="s">
-        <v>124</v>
-      </c>
-      <c r="C78" s="13" t="s">
-        <v>125</v>
-      </c>
-      <c r="D78" s="13"/>
-    </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A79" s="11">
-        <v>74</v>
-      </c>
-      <c r="B79" s="13" t="s">
-        <v>126</v>
-      </c>
-      <c r="C79" s="13" t="s">
-        <v>127</v>
-      </c>
-      <c r="D79" s="13"/>
-    </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A80" s="11">
-        <v>75</v>
-      </c>
-      <c r="B80" s="13" t="s">
-        <v>128</v>
-      </c>
-      <c r="C80" s="13" t="s">
-        <v>129</v>
-      </c>
-      <c r="D80" s="13"/>
-    </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A81" s="11">
-        <v>76</v>
-      </c>
-      <c r="B81" s="13" t="s">
-        <v>130</v>
-      </c>
-      <c r="C81" s="13" t="s">
-        <v>131</v>
-      </c>
-      <c r="D81" s="13"/>
-    </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A82" s="11">
-        <v>77</v>
-      </c>
-      <c r="B82" s="13" t="s">
-        <v>132</v>
-      </c>
-      <c r="C82" s="13" t="s">
-        <v>133</v>
-      </c>
-      <c r="D82" s="13"/>
-    </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A83" s="11">
-        <v>78</v>
-      </c>
-      <c r="B83" s="13" t="s">
-        <v>134</v>
-      </c>
-      <c r="C83" s="13" t="s">
-        <v>135</v>
-      </c>
-      <c r="D83" s="13"/>
-    </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A84" s="11">
-        <v>79</v>
-      </c>
-      <c r="B84" s="13" t="s">
-        <v>136</v>
-      </c>
-      <c r="C84" s="13" t="s">
-        <v>137</v>
-      </c>
-      <c r="D84" s="13"/>
-    </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A85" s="11">
-        <v>80</v>
-      </c>
-      <c r="B85" s="13" t="s">
-        <v>138</v>
-      </c>
-      <c r="C85" s="13" t="s">
-        <v>139</v>
-      </c>
-      <c r="D85" s="13"/>
-    </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A86" s="11">
-        <v>81</v>
-      </c>
-      <c r="B86" s="13" t="s">
-        <v>140</v>
-      </c>
-      <c r="C86" s="13" t="s">
-        <v>141</v>
-      </c>
-      <c r="D86" s="13"/>
-    </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A87" s="11">
-        <v>82</v>
-      </c>
-      <c r="B87" s="13" t="s">
-        <v>249</v>
-      </c>
-      <c r="C87" s="13" t="s">
-        <v>248</v>
-      </c>
-      <c r="D87" s="13"/>
-    </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A88" s="11">
-        <v>83</v>
-      </c>
-      <c r="B88" s="13" t="s">
-        <v>142</v>
-      </c>
-      <c r="C88" s="13" t="s">
-        <v>143</v>
-      </c>
-      <c r="D88" s="13"/>
-    </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A89" s="11">
-        <v>84</v>
-      </c>
-      <c r="B89" s="13" t="s">
-        <v>144</v>
-      </c>
-      <c r="C89" s="13" t="s">
-        <v>145</v>
-      </c>
-      <c r="D89" s="13"/>
-    </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A90" s="11">
-        <v>85</v>
-      </c>
-      <c r="B90" s="13" t="s">
-        <v>146</v>
-      </c>
-      <c r="C90" s="13" t="s">
-        <v>147</v>
-      </c>
-      <c r="D90" s="13"/>
-    </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A91" s="11">
-        <v>86</v>
-      </c>
-      <c r="B91" s="13" t="s">
-        <v>148</v>
-      </c>
-      <c r="C91" s="13" t="s">
-        <v>149</v>
-      </c>
-      <c r="D91" s="13"/>
-    </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A92" s="11">
-        <v>87</v>
-      </c>
-      <c r="B92" s="13" t="s">
-        <v>150</v>
-      </c>
-      <c r="C92" s="13" t="s">
-        <v>151</v>
-      </c>
-      <c r="D92" s="13"/>
-    </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A93" s="11">
-        <v>88</v>
-      </c>
-      <c r="B93" s="13" t="s">
-        <v>152</v>
-      </c>
-      <c r="C93" s="13" t="s">
-        <v>153</v>
-      </c>
-      <c r="D93" s="13"/>
-    </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A94" s="11">
-        <v>89</v>
-      </c>
-      <c r="B94" s="13" t="s">
-        <v>154</v>
-      </c>
-      <c r="C94" s="13" t="s">
-        <v>155</v>
-      </c>
-      <c r="D94" s="13"/>
-    </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A95" s="11">
-        <v>90</v>
-      </c>
-      <c r="B95" s="13" t="s">
-        <v>251</v>
-      </c>
-      <c r="C95" s="13" t="s">
-        <v>250</v>
-      </c>
-      <c r="D95" s="13"/>
-    </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A96" s="11">
-        <v>91</v>
-      </c>
-      <c r="B96" s="13" t="s">
-        <v>156</v>
-      </c>
-      <c r="C96" s="13" t="s">
-        <v>157</v>
-      </c>
-      <c r="D96" s="13"/>
-    </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A97" s="11">
-        <v>92</v>
-      </c>
-      <c r="B97" s="13" t="s">
-        <v>158</v>
-      </c>
-      <c r="C97" s="13" t="s">
-        <v>31</v>
-      </c>
-      <c r="D97" s="13"/>
-    </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A98" s="11">
-        <v>93</v>
-      </c>
-      <c r="B98" s="13" t="s">
-        <v>159</v>
-      </c>
-      <c r="C98" s="13" t="s">
-        <v>160</v>
-      </c>
-      <c r="D98" s="13"/>
-    </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A99" s="11">
-        <v>94</v>
-      </c>
-      <c r="B99" s="13" t="s">
-        <v>161</v>
-      </c>
-      <c r="C99" s="13" t="s">
-        <v>162</v>
-      </c>
-      <c r="D99" s="13"/>
-    </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A100" s="11">
-        <v>95</v>
-      </c>
-      <c r="B100" s="13" t="s">
-        <v>163</v>
-      </c>
-      <c r="C100" s="13" t="s">
-        <v>164</v>
-      </c>
-      <c r="D100" s="13"/>
-    </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A101" s="11">
-        <v>96</v>
-      </c>
-      <c r="B101" s="13" t="s">
-        <v>165</v>
-      </c>
-      <c r="C101" s="13" t="s">
-        <v>166</v>
-      </c>
-      <c r="D101" s="13"/>
-    </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A102" s="11">
-        <v>97</v>
-      </c>
-      <c r="B102" s="13" t="s">
-        <v>167</v>
-      </c>
-      <c r="C102" s="13" t="s">
-        <v>168</v>
-      </c>
-      <c r="D102" s="13"/>
-    </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A103" s="11">
-        <v>98</v>
-      </c>
-      <c r="B103" s="13" t="s">
-        <v>169</v>
-      </c>
-      <c r="C103" s="13" t="s">
-        <v>170</v>
-      </c>
-      <c r="D103" s="13"/>
-    </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A104" s="11">
-        <v>99</v>
-      </c>
-      <c r="B104" s="13" t="s">
-        <v>171</v>
-      </c>
-      <c r="C104" s="13" t="s">
-        <v>172</v>
-      </c>
-      <c r="D104" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -4483,10 +3249,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8F4DED6-DEC4-47B2-9782-0B0DA58E7480}">
-  <dimension ref="A1:H172"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="18" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:H274"/>
+  <sheetFormatPr defaultColWidth="10.85546875" defaultRowHeight="18.5" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A1" s="5" t="s">
         <v>269</v>
       </c>
@@ -4498,23 +3264,23 @@
       <c r="G1" s="3"/>
       <c r="H1" s="3"/>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A2" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="B2" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="10"/>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A3" s="17">
+      <c r="C2" s="19"/>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A3" s="6">
         <v>42</v>
       </c>
-      <c r="B3" s="18" t="s">
+      <c r="B3" s="12" t="s">
         <v>289</v>
       </c>
-      <c r="C3" s="19" t="s">
+      <c r="C3" s="13" t="s">
         <v>290</v>
       </c>
       <c r="D3" s="8" t="s">
@@ -4524,14 +3290,14 @@
         <v>271</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A4" s="17">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A4" s="6">
         <v>39</v>
       </c>
-      <c r="B4" s="18" t="s">
+      <c r="B4" s="12" t="s">
         <v>291</v>
       </c>
-      <c r="C4" s="19" t="s">
+      <c r="C4" s="13" t="s">
         <v>292</v>
       </c>
       <c r="D4" s="8" t="s">
@@ -4541,14 +3307,14 @@
         <v>271</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="36" x14ac:dyDescent="0.35">
-      <c r="A5" s="17">
+    <row r="5" spans="1:8" ht="37" x14ac:dyDescent="0.45">
+      <c r="A5" s="6">
         <v>15</v>
       </c>
-      <c r="B5" s="18" t="s">
+      <c r="B5" s="12" t="s">
         <v>293</v>
       </c>
-      <c r="C5" s="19" t="s">
+      <c r="C5" s="13" t="s">
         <v>298</v>
       </c>
       <c r="D5" s="8" t="s">
@@ -4558,14 +3324,14 @@
         <v>271</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A6" s="17">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A6" s="6">
         <v>33</v>
       </c>
-      <c r="B6" s="18" t="s">
+      <c r="B6" s="12" t="s">
         <v>294</v>
       </c>
-      <c r="C6" s="19" t="s">
+      <c r="C6" s="13" t="s">
         <v>295</v>
       </c>
       <c r="D6" s="8" t="s">
@@ -4575,14 +3341,14 @@
         <v>271</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A7" s="17">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A7" s="6">
         <v>35</v>
       </c>
-      <c r="B7" s="18" t="s">
+      <c r="B7" s="12" t="s">
         <v>296</v>
       </c>
-      <c r="C7" s="19" t="s">
+      <c r="C7" s="13" t="s">
         <v>297</v>
       </c>
       <c r="D7" s="8" t="s">
@@ -4592,14 +3358,14 @@
         <v>271</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="36" x14ac:dyDescent="0.35">
-      <c r="A8" s="17">
+    <row r="8" spans="1:8" ht="37" x14ac:dyDescent="0.45">
+      <c r="A8" s="6">
         <v>34</v>
       </c>
-      <c r="B8" s="18" t="s">
+      <c r="B8" s="12" t="s">
         <v>299</v>
       </c>
-      <c r="C8" s="19" t="s">
+      <c r="C8" s="13" t="s">
         <v>300</v>
       </c>
       <c r="D8" s="8" t="s">
@@ -4609,14 +3375,14 @@
         <v>271</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A9" s="17">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A9" s="6">
         <v>35</v>
       </c>
-      <c r="B9" s="18" t="s">
+      <c r="B9" s="12" t="s">
         <v>301</v>
       </c>
-      <c r="C9" s="19" t="s">
+      <c r="C9" s="13" t="s">
         <v>302</v>
       </c>
       <c r="D9" s="8" t="s">
@@ -4626,14 +3392,14 @@
         <v>271</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A10" s="17">
+    <row r="10" spans="1:8" ht="37" x14ac:dyDescent="0.45">
+      <c r="A10" s="6">
         <v>62</v>
       </c>
-      <c r="B10" s="18" t="s">
+      <c r="B10" s="12" t="s">
         <v>303</v>
       </c>
-      <c r="C10" s="19" t="s">
+      <c r="C10" s="13" t="s">
         <v>304</v>
       </c>
       <c r="D10" s="8" t="s">
@@ -4643,14 +3409,14 @@
         <v>271</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A11" s="17">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A11" s="6">
         <v>29</v>
       </c>
-      <c r="B11" s="18" t="s">
+      <c r="B11" s="12" t="s">
         <v>305</v>
       </c>
-      <c r="C11" s="19" t="s">
+      <c r="C11" s="13" t="s">
         <v>306</v>
       </c>
       <c r="D11" s="8" t="s">
@@ -4660,14 +3426,14 @@
         <v>271</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A12" s="17">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A12" s="6">
         <v>16</v>
       </c>
-      <c r="B12" s="18" t="s">
+      <c r="B12" s="12" t="s">
         <v>307</v>
       </c>
-      <c r="C12" s="19" t="s">
+      <c r="C12" s="13" t="s">
         <v>308</v>
       </c>
       <c r="D12" s="8" t="s">
@@ -4677,14 +3443,14 @@
         <v>271</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A13" s="17">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A13" s="6">
         <v>14</v>
       </c>
-      <c r="B13" s="18" t="s">
+      <c r="B13" s="12" t="s">
         <v>309</v>
       </c>
-      <c r="C13" s="19" t="s">
+      <c r="C13" s="13" t="s">
         <v>310</v>
       </c>
       <c r="D13" s="8" t="s">
@@ -4694,14 +3460,14 @@
         <v>271</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="36" x14ac:dyDescent="0.35">
-      <c r="A14" s="17">
+    <row r="14" spans="1:8" ht="37" x14ac:dyDescent="0.45">
+      <c r="A14" s="6">
         <v>82</v>
       </c>
-      <c r="B14" s="18" t="s">
+      <c r="B14" s="12" t="s">
         <v>311</v>
       </c>
-      <c r="C14" s="19" t="s">
+      <c r="C14" s="13" t="s">
         <v>312</v>
       </c>
       <c r="D14" s="8" t="s">
@@ -4711,14 +3477,14 @@
         <v>271</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="36" x14ac:dyDescent="0.35">
-      <c r="A15" s="17">
+    <row r="15" spans="1:8" ht="37" x14ac:dyDescent="0.45">
+      <c r="A15" s="6">
         <v>51</v>
       </c>
-      <c r="B15" s="18" t="s">
+      <c r="B15" s="12" t="s">
         <v>313</v>
       </c>
-      <c r="C15" s="19" t="s">
+      <c r="C15" s="13" t="s">
         <v>314</v>
       </c>
       <c r="D15" s="8" t="s">
@@ -4728,14 +3494,14 @@
         <v>271</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="36" x14ac:dyDescent="0.35">
-      <c r="A16" s="17">
+    <row r="16" spans="1:8" ht="37" x14ac:dyDescent="0.45">
+      <c r="A16" s="6">
         <v>48</v>
       </c>
-      <c r="B16" s="18" t="s">
+      <c r="B16" s="12" t="s">
         <v>315</v>
       </c>
-      <c r="C16" s="19" t="s">
+      <c r="C16" s="13" t="s">
         <v>316</v>
       </c>
       <c r="D16" s="8" t="s">
@@ -4745,14 +3511,14 @@
         <v>271</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="36" x14ac:dyDescent="0.35">
-      <c r="A17" s="17">
+    <row r="17" spans="1:7" ht="37" x14ac:dyDescent="0.45">
+      <c r="A17" s="6">
         <v>47</v>
       </c>
-      <c r="B17" s="18" t="s">
+      <c r="B17" s="12" t="s">
         <v>317</v>
       </c>
-      <c r="C17" s="19" t="s">
+      <c r="C17" s="13" t="s">
         <v>318</v>
       </c>
       <c r="D17" s="8" t="s">
@@ -4762,14 +3528,14 @@
         <v>271</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="36" x14ac:dyDescent="0.35">
-      <c r="A18" s="17">
+    <row r="18" spans="1:7" ht="37" x14ac:dyDescent="0.45">
+      <c r="A18" s="6">
         <v>46</v>
       </c>
-      <c r="B18" s="18" t="s">
+      <c r="B18" s="12" t="s">
         <v>319</v>
       </c>
-      <c r="C18" s="19" t="s">
+      <c r="C18" s="13" t="s">
         <v>320</v>
       </c>
       <c r="D18" s="8" t="s">
@@ -4779,14 +3545,14 @@
         <v>271</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="36" x14ac:dyDescent="0.35">
-      <c r="A19" s="17">
+    <row r="19" spans="1:7" ht="37" x14ac:dyDescent="0.45">
+      <c r="A19" s="6">
         <v>83</v>
       </c>
-      <c r="B19" s="13" t="s">
+      <c r="B19" t="s">
         <v>667</v>
       </c>
-      <c r="C19" s="13" t="s">
+      <c r="C19" t="s">
         <v>668</v>
       </c>
       <c r="D19" s="8" t="s">
@@ -4796,14 +3562,14 @@
         <v>271</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="36" x14ac:dyDescent="0.35">
-      <c r="A20" s="17">
+    <row r="20" spans="1:7" ht="37" x14ac:dyDescent="0.45">
+      <c r="A20" s="6">
         <v>45</v>
       </c>
-      <c r="B20" s="18" t="s">
+      <c r="B20" s="12" t="s">
         <v>321</v>
       </c>
-      <c r="C20" s="19" t="s">
+      <c r="C20" s="13" t="s">
         <v>322</v>
       </c>
       <c r="D20" s="8" t="s">
@@ -4813,14 +3579,14 @@
         <v>271</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A21" s="17">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A21" s="6">
         <v>84</v>
       </c>
-      <c r="B21" s="18" t="s">
+      <c r="B21" s="12" t="s">
         <v>323</v>
       </c>
-      <c r="C21" s="19" t="s">
+      <c r="C21" s="13" t="s">
         <v>324</v>
       </c>
       <c r="D21" s="8" t="s">
@@ -4830,14 +3596,14 @@
         <v>271</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A22" s="17">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A22" s="6">
         <v>24</v>
       </c>
-      <c r="B22" s="18" t="s">
+      <c r="B22" s="12" t="s">
         <v>325</v>
       </c>
-      <c r="C22" s="19" t="s">
+      <c r="C22" s="13" t="s">
         <v>326</v>
       </c>
       <c r="D22" s="8" t="s">
@@ -4847,14 +3613,14 @@
         <v>271</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A23" s="17">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A23" s="6">
         <v>32</v>
       </c>
-      <c r="B23" s="18" t="s">
+      <c r="B23" s="12" t="s">
         <v>327</v>
       </c>
-      <c r="C23" s="19" t="s">
+      <c r="C23" s="13" t="s">
         <v>328</v>
       </c>
       <c r="D23" s="8" t="s">
@@ -4864,14 +3630,14 @@
         <v>271</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A24" s="17">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A24" s="6">
         <v>31</v>
       </c>
-      <c r="B24" s="18" t="s">
+      <c r="B24" s="12" t="s">
         <v>329</v>
       </c>
-      <c r="C24" s="19" t="s">
+      <c r="C24" s="13" t="s">
         <v>330</v>
       </c>
       <c r="D24" s="8" t="s">
@@ -4881,14 +3647,14 @@
         <v>271</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="36" x14ac:dyDescent="0.35">
-      <c r="A25" s="17">
+    <row r="25" spans="1:7" ht="37" x14ac:dyDescent="0.45">
+      <c r="A25" s="6">
         <v>55</v>
       </c>
-      <c r="B25" s="18" t="s">
+      <c r="B25" s="12" t="s">
         <v>331</v>
       </c>
-      <c r="C25" s="19" t="s">
+      <c r="C25" s="13" t="s">
         <v>332</v>
       </c>
       <c r="D25" s="8" t="s">
@@ -4897,15 +3663,16 @@
       <c r="E25" s="6" t="s">
         <v>271</v>
       </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A26" s="17">
+      <c r="G25" s="20"/>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A26" s="6">
         <v>45</v>
       </c>
-      <c r="B26" s="18" t="s">
+      <c r="B26" s="12" t="s">
         <v>333</v>
       </c>
-      <c r="C26" s="19" t="s">
+      <c r="C26" s="13" t="s">
         <v>334</v>
       </c>
       <c r="D26" s="8" t="s">
@@ -4915,14 +3682,14 @@
         <v>271</v>
       </c>
     </row>
-    <row r="27" spans="1:5" ht="36" x14ac:dyDescent="0.35">
-      <c r="A27" s="17">
+    <row r="27" spans="1:7" ht="37" x14ac:dyDescent="0.45">
+      <c r="A27" s="6">
         <v>5</v>
       </c>
-      <c r="B27" s="18" t="s">
+      <c r="B27" s="12" t="s">
         <v>335</v>
       </c>
-      <c r="C27" s="19" t="s">
+      <c r="C27" s="13" t="s">
         <v>336</v>
       </c>
       <c r="D27" s="8" t="s">
@@ -4932,14 +3699,14 @@
         <v>271</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A28" s="17">
+    <row r="28" spans="1:7" ht="37" x14ac:dyDescent="0.45">
+      <c r="A28" s="6">
         <v>73</v>
       </c>
-      <c r="B28" s="18" t="s">
+      <c r="B28" s="12" t="s">
         <v>337</v>
       </c>
-      <c r="C28" s="19" t="s">
+      <c r="C28" s="13" t="s">
         <v>338</v>
       </c>
       <c r="D28" s="8" t="s">
@@ -4949,14 +3716,14 @@
         <v>271</v>
       </c>
     </row>
-    <row r="29" spans="1:5" ht="36" x14ac:dyDescent="0.35">
-      <c r="A29" s="17">
+    <row r="29" spans="1:7" ht="37" x14ac:dyDescent="0.45">
+      <c r="A29" s="6">
         <v>43</v>
       </c>
-      <c r="B29" s="18" t="s">
+      <c r="B29" s="12" t="s">
         <v>339</v>
       </c>
-      <c r="C29" s="19" t="s">
+      <c r="C29" s="13" t="s">
         <v>340</v>
       </c>
       <c r="D29" s="8" t="s">
@@ -4966,14 +3733,14 @@
         <v>271</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="36" x14ac:dyDescent="0.35">
-      <c r="A30" s="17">
+    <row r="30" spans="1:7" ht="37" x14ac:dyDescent="0.45">
+      <c r="A30" s="6">
         <v>44</v>
       </c>
-      <c r="B30" s="18" t="s">
+      <c r="B30" s="12" t="s">
         <v>341</v>
       </c>
-      <c r="C30" s="19" t="s">
+      <c r="C30" s="13" t="s">
         <v>342</v>
       </c>
       <c r="D30" s="8" t="s">
@@ -4983,14 +3750,14 @@
         <v>271</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A31" s="17">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A31" s="6">
         <v>22</v>
       </c>
-      <c r="B31" s="18" t="s">
+      <c r="B31" s="12" t="s">
         <v>343</v>
       </c>
-      <c r="C31" s="19" t="s">
+      <c r="C31" s="13" t="s">
         <v>344</v>
       </c>
       <c r="D31" s="8" t="s">
@@ -5000,14 +3767,14 @@
         <v>271</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A32" s="17">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A32" s="6">
         <v>23</v>
       </c>
-      <c r="B32" s="18" t="s">
+      <c r="B32" s="12" t="s">
         <v>345</v>
       </c>
-      <c r="C32" s="19" t="s">
+      <c r="C32" s="13" t="s">
         <v>346</v>
       </c>
       <c r="D32" s="8" t="s">
@@ -5017,14 +3784,14 @@
         <v>271</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A33" s="17">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A33" s="6">
         <v>26</v>
       </c>
-      <c r="B33" s="18" t="s">
+      <c r="B33" s="12" t="s">
         <v>347</v>
       </c>
-      <c r="C33" s="19" t="s">
+      <c r="C33" s="13" t="s">
         <v>348</v>
       </c>
       <c r="D33" s="8" t="s">
@@ -5034,14 +3801,14 @@
         <v>271</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A34" s="17">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A34" s="6">
         <v>24</v>
       </c>
-      <c r="B34" s="18" t="s">
+      <c r="B34" s="12" t="s">
         <v>349</v>
       </c>
-      <c r="C34" s="19" t="s">
+      <c r="C34" s="13" t="s">
         <v>350</v>
       </c>
       <c r="D34" s="8" t="s">
@@ -5051,14 +3818,14 @@
         <v>271</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A35" s="17">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A35" s="6">
         <v>25</v>
       </c>
-      <c r="B35" s="18" t="s">
+      <c r="B35" s="12" t="s">
         <v>351</v>
       </c>
-      <c r="C35" s="19" t="s">
+      <c r="C35" s="13" t="s">
         <v>352</v>
       </c>
       <c r="D35" s="8" t="s">
@@ -5068,14 +3835,14 @@
         <v>271</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A36" s="17">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A36" s="6">
         <v>36</v>
       </c>
-      <c r="B36" s="18" t="s">
+      <c r="B36" s="12" t="s">
         <v>353</v>
       </c>
-      <c r="C36" s="19" t="s">
+      <c r="C36" s="13" t="s">
         <v>354</v>
       </c>
       <c r="D36" s="8" t="s">
@@ -5085,14 +3852,14 @@
         <v>271</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A37" s="17">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A37" s="6">
         <v>21</v>
       </c>
-      <c r="B37" s="18" t="s">
+      <c r="B37" s="12" t="s">
         <v>355</v>
       </c>
-      <c r="C37" s="19" t="s">
+      <c r="C37" s="13" t="s">
         <v>356</v>
       </c>
       <c r="D37" s="8" t="s">
@@ -5102,14 +3869,14 @@
         <v>271</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A38" s="17">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A38" s="6">
         <v>99</v>
       </c>
-      <c r="B38" s="18" t="s">
+      <c r="B38" s="12" t="s">
         <v>357</v>
       </c>
-      <c r="C38" s="19" t="s">
+      <c r="C38" s="13" t="s">
         <v>358</v>
       </c>
       <c r="D38" s="8" t="s">
@@ -5119,14 +3886,14 @@
         <v>271</v>
       </c>
     </row>
-    <row r="39" spans="1:5" ht="36" x14ac:dyDescent="0.35">
-      <c r="A39" s="17">
+    <row r="39" spans="1:5" ht="37" x14ac:dyDescent="0.45">
+      <c r="A39" s="6">
         <v>84</v>
       </c>
-      <c r="B39" s="18" t="s">
+      <c r="B39" s="12" t="s">
         <v>359</v>
       </c>
-      <c r="C39" s="19" t="s">
+      <c r="C39" s="13" t="s">
         <v>360</v>
       </c>
       <c r="D39" s="8" t="s">
@@ -5136,14 +3903,14 @@
         <v>271</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A40" s="17">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A40" s="6">
         <v>27</v>
       </c>
-      <c r="B40" s="18" t="s">
+      <c r="B40" s="12" t="s">
         <v>361</v>
       </c>
-      <c r="C40" s="19" t="s">
+      <c r="C40" s="13" t="s">
         <v>362</v>
       </c>
       <c r="D40" s="8" t="s">
@@ -5153,14 +3920,14 @@
         <v>271</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A41" s="17">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A41" s="6">
         <v>33</v>
       </c>
-      <c r="B41" s="18" t="s">
+      <c r="B41" s="12" t="s">
         <v>363</v>
       </c>
-      <c r="C41" s="19" t="s">
+      <c r="C41" s="13" t="s">
         <v>364</v>
       </c>
       <c r="D41" s="8" t="s">
@@ -5170,14 +3937,14 @@
         <v>271</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A42" s="17">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A42" s="6">
         <v>96</v>
       </c>
-      <c r="B42" s="18" t="s">
+      <c r="B42" s="12" t="s">
         <v>365</v>
       </c>
-      <c r="C42" s="19" t="s">
+      <c r="C42" s="13" t="s">
         <v>366</v>
       </c>
       <c r="D42" s="8" t="s">
@@ -5187,14 +3954,14 @@
         <v>271</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A43" s="17">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A43" s="6">
         <v>11</v>
       </c>
-      <c r="B43" s="18" t="s">
+      <c r="B43" s="12" t="s">
         <v>367</v>
       </c>
-      <c r="C43" s="19" t="s">
+      <c r="C43" s="13" t="s">
         <v>368</v>
       </c>
       <c r="D43" s="8" t="s">
@@ -5204,14 +3971,14 @@
         <v>271</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A44" s="17">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A44" s="6">
         <v>34</v>
       </c>
-      <c r="B44" s="18" t="s">
+      <c r="B44" s="12" t="s">
         <v>369</v>
       </c>
-      <c r="C44" s="19" t="s">
+      <c r="C44" s="13" t="s">
         <v>370</v>
       </c>
       <c r="D44" s="8" t="s">
@@ -5221,14 +3988,14 @@
         <v>271</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A45" s="17">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A45" s="6">
         <v>20</v>
       </c>
-      <c r="B45" s="18" t="s">
+      <c r="B45" s="12" t="s">
         <v>371</v>
       </c>
-      <c r="C45" s="19" t="s">
+      <c r="C45" s="13" t="s">
         <v>372</v>
       </c>
       <c r="D45" s="8" t="s">
@@ -5238,14 +4005,14 @@
         <v>271</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A46" s="17">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A46" s="6">
         <v>83</v>
       </c>
-      <c r="B46" s="18" t="s">
+      <c r="B46" s="12" t="s">
         <v>373</v>
       </c>
-      <c r="C46" s="19" t="s">
+      <c r="C46" s="13" t="s">
         <v>374</v>
       </c>
       <c r="D46" s="8" t="s">
@@ -5255,14 +4022,14 @@
         <v>271</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A47" s="17">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A47" s="6">
         <v>95</v>
       </c>
-      <c r="B47" s="18" t="s">
+      <c r="B47" s="12" t="s">
         <v>375</v>
       </c>
-      <c r="C47" s="19" t="s">
+      <c r="C47" s="13" t="s">
         <v>376</v>
       </c>
       <c r="D47" s="8" t="s">
@@ -5272,14 +4039,14 @@
         <v>271</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A48" s="17">
+    <row r="48" spans="1:5" ht="37" x14ac:dyDescent="0.45">
+      <c r="A48" s="6">
         <v>56</v>
       </c>
-      <c r="B48" s="18" t="s">
+      <c r="B48" s="12" t="s">
         <v>377</v>
       </c>
-      <c r="C48" s="19" t="s">
+      <c r="C48" s="13" t="s">
         <v>378</v>
       </c>
       <c r="D48" s="8" t="s">
@@ -5289,14 +4056,14 @@
         <v>271</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A49" s="17">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A49" s="6">
         <v>86</v>
       </c>
-      <c r="B49" s="18" t="s">
+      <c r="B49" s="12" t="s">
         <v>379</v>
       </c>
-      <c r="C49" s="19" t="s">
+      <c r="C49" s="13" t="s">
         <v>380</v>
       </c>
       <c r="D49" s="8" t="s">
@@ -5306,14 +4073,14 @@
         <v>271</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A50" s="17">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A50" s="6">
         <v>95</v>
       </c>
-      <c r="B50" s="18" t="s">
+      <c r="B50" s="12" t="s">
         <v>381</v>
       </c>
-      <c r="C50" s="19" t="s">
+      <c r="C50" s="13" t="s">
         <v>382</v>
       </c>
       <c r="D50" s="8" t="s">
@@ -5323,14 +4090,14 @@
         <v>271</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A51" s="17">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A51" s="6">
         <v>98</v>
       </c>
-      <c r="B51" s="18" t="s">
+      <c r="B51" s="12" t="s">
         <v>383</v>
       </c>
-      <c r="C51" s="19" t="s">
+      <c r="C51" s="13" t="s">
         <v>384</v>
       </c>
       <c r="D51" s="8" t="s">
@@ -5340,15 +4107,15 @@
         <v>271</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A52" s="17">
+    <row r="52" spans="1:7" ht="37" x14ac:dyDescent="0.45">
+      <c r="A52" s="6">
         <v>55</v>
       </c>
-      <c r="B52" s="13" t="s">
-        <v>669</v>
-      </c>
-      <c r="C52" s="13" t="s">
-        <v>670</v>
+      <c r="B52" t="s">
+        <v>676</v>
+      </c>
+      <c r="C52" t="s">
+        <v>677</v>
       </c>
       <c r="D52" s="8" t="s">
         <v>276</v>
@@ -5356,15 +4123,16 @@
       <c r="E52" s="6" t="s">
         <v>271</v>
       </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A53" s="17">
+      <c r="G52" s="20"/>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A53" s="6">
         <v>82</v>
       </c>
-      <c r="B53" s="18" t="s">
+      <c r="B53" s="12" t="s">
         <v>385</v>
       </c>
-      <c r="C53" s="19" t="s">
+      <c r="C53" s="13" t="s">
         <v>386</v>
       </c>
       <c r="D53" s="8" t="s">
@@ -5374,14 +4142,14 @@
         <v>271</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A54" s="17">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.45">
+      <c r="A54" s="6">
         <v>85</v>
       </c>
-      <c r="B54" s="18" t="s">
+      <c r="B54" s="12" t="s">
         <v>387</v>
       </c>
-      <c r="C54" s="19" t="s">
+      <c r="C54" s="13" t="s">
         <v>388</v>
       </c>
       <c r="D54" s="8" t="s">
@@ -5391,14 +4159,14 @@
         <v>271</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A55" s="17">
+    <row r="55" spans="1:7" ht="37" x14ac:dyDescent="0.45">
+      <c r="A55" s="6">
         <v>75</v>
       </c>
-      <c r="B55" s="18" t="s">
+      <c r="B55" s="12" t="s">
         <v>389</v>
       </c>
-      <c r="C55" s="19" t="s">
+      <c r="C55" s="13" t="s">
         <v>390</v>
       </c>
       <c r="D55" s="8" t="s">
@@ -5408,14 +4176,14 @@
         <v>271</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A56" s="17">
+    <row r="56" spans="1:7" ht="37" x14ac:dyDescent="0.45">
+      <c r="A56" s="6">
         <v>64</v>
       </c>
-      <c r="B56" s="18" t="s">
+      <c r="B56" s="12" t="s">
         <v>391</v>
       </c>
-      <c r="C56" s="19" t="s">
+      <c r="C56" s="13" t="s">
         <v>392</v>
       </c>
       <c r="D56" s="8" t="s">
@@ -5425,14 +4193,14 @@
         <v>271</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A57" s="17">
+    <row r="57" spans="1:7" ht="37" x14ac:dyDescent="0.45">
+      <c r="A57" s="6">
         <v>77</v>
       </c>
-      <c r="B57" s="18" t="s">
+      <c r="B57" s="12" t="s">
         <v>393</v>
       </c>
-      <c r="C57" s="19" t="s">
+      <c r="C57" s="13" t="s">
         <v>394</v>
       </c>
       <c r="D57" s="8" t="s">
@@ -5442,14 +4210,14 @@
         <v>271</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A58" s="17">
+    <row r="58" spans="1:7" ht="37" x14ac:dyDescent="0.45">
+      <c r="A58" s="6">
         <v>76</v>
       </c>
-      <c r="B58" s="18" t="s">
+      <c r="B58" s="12" t="s">
         <v>395</v>
       </c>
-      <c r="C58" s="19" t="s">
+      <c r="C58" s="13" t="s">
         <v>396</v>
       </c>
       <c r="D58" s="8" t="s">
@@ -5459,14 +4227,14 @@
         <v>271</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A59" s="17">
+    <row r="59" spans="1:7" ht="37" x14ac:dyDescent="0.45">
+      <c r="A59" s="6">
         <v>68</v>
       </c>
-      <c r="B59" s="18" t="s">
+      <c r="B59" s="12" t="s">
         <v>397</v>
       </c>
-      <c r="C59" s="19" t="s">
+      <c r="C59" s="13" t="s">
         <v>398</v>
       </c>
       <c r="D59" s="8" t="s">
@@ -5476,14 +4244,14 @@
         <v>271</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A60" s="17">
+    <row r="60" spans="1:7" ht="37" x14ac:dyDescent="0.45">
+      <c r="A60" s="6">
         <v>57</v>
       </c>
-      <c r="B60" s="18" t="s">
+      <c r="B60" s="12" t="s">
         <v>399</v>
       </c>
-      <c r="C60" s="19" t="s">
+      <c r="C60" s="13" t="s">
         <v>400</v>
       </c>
       <c r="D60" s="8" t="s">
@@ -5493,14 +4261,14 @@
         <v>271</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A61" s="17">
+    <row r="61" spans="1:7" ht="37" x14ac:dyDescent="0.45">
+      <c r="A61" s="6">
         <v>67</v>
       </c>
-      <c r="B61" s="18" t="s">
+      <c r="B61" s="12" t="s">
         <v>401</v>
       </c>
-      <c r="C61" s="19" t="s">
+      <c r="C61" s="13" t="s">
         <v>402</v>
       </c>
       <c r="D61" s="8" t="s">
@@ -5510,14 +4278,14 @@
         <v>271</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A62" s="17">
+    <row r="62" spans="1:7" ht="37" x14ac:dyDescent="0.45">
+      <c r="A62" s="6">
         <v>63</v>
       </c>
-      <c r="B62" s="18" t="s">
+      <c r="B62" s="12" t="s">
         <v>403</v>
       </c>
-      <c r="C62" s="19" t="s">
+      <c r="C62" s="13" t="s">
         <v>404</v>
       </c>
       <c r="D62" s="8" t="s">
@@ -5527,14 +4295,14 @@
         <v>271</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A63" s="17">
+    <row r="63" spans="1:7" ht="37" x14ac:dyDescent="0.45">
+      <c r="A63" s="6">
         <v>66</v>
       </c>
-      <c r="B63" s="18" t="s">
+      <c r="B63" s="12" t="s">
         <v>405</v>
       </c>
-      <c r="C63" s="19" t="s">
+      <c r="C63" s="13" t="s">
         <v>406</v>
       </c>
       <c r="D63" s="8" t="s">
@@ -5544,14 +4312,14 @@
         <v>271</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A64" s="17">
+    <row r="64" spans="1:7" ht="37" x14ac:dyDescent="0.45">
+      <c r="A64" s="6">
         <v>59</v>
       </c>
-      <c r="B64" s="18" t="s">
+      <c r="B64" s="12" t="s">
         <v>407</v>
       </c>
-      <c r="C64" s="19" t="s">
+      <c r="C64" s="13" t="s">
         <v>408</v>
       </c>
       <c r="D64" s="8" t="s">
@@ -5561,14 +4329,14 @@
         <v>271</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A65" s="17">
+    <row r="65" spans="1:5" ht="37" x14ac:dyDescent="0.45">
+      <c r="A65" s="6">
         <v>54</v>
       </c>
-      <c r="B65" s="18" t="s">
+      <c r="B65" s="12" t="s">
         <v>409</v>
       </c>
-      <c r="C65" s="19" t="s">
+      <c r="C65" s="13" t="s">
         <v>410</v>
       </c>
       <c r="D65" s="8" t="s">
@@ -5578,14 +4346,14 @@
         <v>271</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A66" s="17">
+    <row r="66" spans="1:5" ht="37" x14ac:dyDescent="0.45">
+      <c r="A66" s="6">
         <v>61</v>
       </c>
-      <c r="B66" s="18" t="s">
+      <c r="B66" s="12" t="s">
         <v>411</v>
       </c>
-      <c r="C66" s="19" t="s">
+      <c r="C66" s="13" t="s">
         <v>412</v>
       </c>
       <c r="D66" s="8" t="s">
@@ -5595,14 +4363,14 @@
         <v>271</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A67" s="17">
+    <row r="67" spans="1:5" ht="37" x14ac:dyDescent="0.45">
+      <c r="A67" s="6">
         <v>60</v>
       </c>
-      <c r="B67" s="18" t="s">
+      <c r="B67" s="12" t="s">
         <v>413</v>
       </c>
-      <c r="C67" s="19" t="s">
+      <c r="C67" s="13" t="s">
         <v>414</v>
       </c>
       <c r="D67" s="8" t="s">
@@ -5612,14 +4380,14 @@
         <v>271</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A68" s="17">
+    <row r="68" spans="1:5" ht="37" x14ac:dyDescent="0.45">
+      <c r="A68" s="6">
         <v>58</v>
       </c>
-      <c r="B68" s="18" t="s">
+      <c r="B68" s="12" t="s">
         <v>415</v>
       </c>
-      <c r="C68" s="19" t="s">
+      <c r="C68" s="13" t="s">
         <v>416</v>
       </c>
       <c r="D68" s="8" t="s">
@@ -5629,14 +4397,14 @@
         <v>271</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A69" s="17">
+    <row r="69" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A69" s="6">
         <v>80</v>
       </c>
-      <c r="B69" s="18" t="s">
+      <c r="B69" s="12" t="s">
         <v>417</v>
       </c>
-      <c r="C69" s="19" t="s">
+      <c r="C69" s="13" t="s">
         <v>418</v>
       </c>
       <c r="D69" s="8" t="s">
@@ -5646,14 +4414,14 @@
         <v>271</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A70" s="17">
+    <row r="70" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A70" s="6">
         <v>81</v>
       </c>
-      <c r="B70" s="18" t="s">
+      <c r="B70" s="12" t="s">
         <v>419</v>
       </c>
-      <c r="C70" s="19" t="s">
+      <c r="C70" s="13" t="s">
         <v>420</v>
       </c>
       <c r="D70" s="8" t="s">
@@ -5663,14 +4431,14 @@
         <v>271</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A71" s="17">
+    <row r="71" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A71" s="6">
         <v>95</v>
       </c>
-      <c r="B71" s="18" t="s">
+      <c r="B71" s="12" t="s">
         <v>421</v>
       </c>
-      <c r="C71" s="19" t="s">
+      <c r="C71" s="13" t="s">
         <v>422</v>
       </c>
       <c r="D71" s="8" t="s">
@@ -5680,14 +4448,14 @@
         <v>271</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A72" s="17">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A72" s="6">
         <v>96</v>
       </c>
-      <c r="B72" s="18" t="s">
+      <c r="B72" s="12" t="s">
         <v>423</v>
       </c>
-      <c r="C72" s="19" t="s">
+      <c r="C72" s="13" t="s">
         <v>424</v>
       </c>
       <c r="D72" s="8" t="s">
@@ -5697,14 +4465,14 @@
         <v>271</v>
       </c>
     </row>
-    <row r="73" spans="1:5" ht="36" x14ac:dyDescent="0.35">
-      <c r="A73" s="17">
+    <row r="73" spans="1:5" ht="37" x14ac:dyDescent="0.45">
+      <c r="A73" s="6">
         <v>1</v>
       </c>
-      <c r="B73" s="18" t="s">
+      <c r="B73" s="12" t="s">
         <v>425</v>
       </c>
-      <c r="C73" s="19" t="s">
+      <c r="C73" s="13" t="s">
         <v>426</v>
       </c>
       <c r="D73" s="8" t="s">
@@ -5714,14 +4482,14 @@
         <v>271</v>
       </c>
     </row>
-    <row r="74" spans="1:5" ht="36" x14ac:dyDescent="0.35">
-      <c r="A74" s="17">
+    <row r="74" spans="1:5" ht="37" x14ac:dyDescent="0.45">
+      <c r="A74" s="6">
         <v>2</v>
       </c>
-      <c r="B74" s="18" t="s">
+      <c r="B74" s="12" t="s">
         <v>427</v>
       </c>
-      <c r="C74" s="19" t="s">
+      <c r="C74" s="13" t="s">
         <v>428</v>
       </c>
       <c r="D74" s="8" t="s">
@@ -5731,14 +4499,14 @@
         <v>271</v>
       </c>
     </row>
-    <row r="75" spans="1:5" ht="36" x14ac:dyDescent="0.35">
-      <c r="A75" s="17">
+    <row r="75" spans="1:5" ht="37" x14ac:dyDescent="0.45">
+      <c r="A75" s="6">
         <v>6</v>
       </c>
-      <c r="B75" s="18" t="s">
+      <c r="B75" s="12" t="s">
         <v>429</v>
       </c>
-      <c r="C75" s="19" t="s">
+      <c r="C75" s="13" t="s">
         <v>430</v>
       </c>
       <c r="D75" s="8" t="s">
@@ -5748,14 +4516,14 @@
         <v>271</v>
       </c>
     </row>
-    <row r="76" spans="1:5" ht="36" x14ac:dyDescent="0.35">
-      <c r="A76" s="17">
+    <row r="76" spans="1:5" ht="37" x14ac:dyDescent="0.45">
+      <c r="A76" s="6">
         <v>9</v>
       </c>
-      <c r="B76" s="18" t="s">
+      <c r="B76" s="12" t="s">
         <v>431</v>
       </c>
-      <c r="C76" s="19" t="s">
+      <c r="C76" s="13" t="s">
         <v>432</v>
       </c>
       <c r="D76" s="8" t="s">
@@ -5765,14 +4533,14 @@
         <v>271</v>
       </c>
     </row>
-    <row r="77" spans="1:5" ht="36" x14ac:dyDescent="0.35">
-      <c r="A77" s="17">
+    <row r="77" spans="1:5" ht="37" x14ac:dyDescent="0.45">
+      <c r="A77" s="6">
         <v>7</v>
       </c>
-      <c r="B77" s="18" t="s">
+      <c r="B77" s="12" t="s">
         <v>433</v>
       </c>
-      <c r="C77" s="19" t="s">
+      <c r="C77" s="13" t="s">
         <v>434</v>
       </c>
       <c r="D77" s="8" t="s">
@@ -5782,14 +4550,14 @@
         <v>271</v>
       </c>
     </row>
-    <row r="78" spans="1:5" ht="36" x14ac:dyDescent="0.35">
-      <c r="A78" s="17">
+    <row r="78" spans="1:5" ht="37" x14ac:dyDescent="0.45">
+      <c r="A78" s="6">
         <v>8</v>
       </c>
-      <c r="B78" s="18" t="s">
+      <c r="B78" s="12" t="s">
         <v>435</v>
       </c>
-      <c r="C78" s="19" t="s">
+      <c r="C78" s="13" t="s">
         <v>436</v>
       </c>
       <c r="D78" s="8" t="s">
@@ -5799,14 +4567,14 @@
         <v>271</v>
       </c>
     </row>
-    <row r="79" spans="1:5" ht="36" x14ac:dyDescent="0.35">
-      <c r="A79" s="20">
+    <row r="79" spans="1:5" ht="37" x14ac:dyDescent="0.45">
+      <c r="A79" s="7">
         <v>3</v>
       </c>
-      <c r="B79" s="21" t="s">
+      <c r="B79" s="14" t="s">
         <v>437</v>
       </c>
-      <c r="C79" s="19" t="s">
+      <c r="C79" s="13" t="s">
         <v>438</v>
       </c>
       <c r="D79" s="9" t="s">
@@ -5816,14 +4584,14 @@
         <v>271</v>
       </c>
     </row>
-    <row r="80" spans="1:5" ht="36" x14ac:dyDescent="0.35">
-      <c r="A80" s="17">
+    <row r="80" spans="1:5" ht="37" x14ac:dyDescent="0.45">
+      <c r="A80" s="6">
         <v>10</v>
       </c>
-      <c r="B80" s="18" t="s">
+      <c r="B80" s="12" t="s">
         <v>439</v>
       </c>
-      <c r="C80" s="19" t="s">
+      <c r="C80" s="13" t="s">
         <v>440</v>
       </c>
       <c r="D80" s="8" t="s">
@@ -5833,14 +4601,14 @@
         <v>271</v>
       </c>
     </row>
-    <row r="81" spans="1:5" ht="36" x14ac:dyDescent="0.35">
-      <c r="A81" s="17">
+    <row r="81" spans="1:5" ht="37" x14ac:dyDescent="0.45">
+      <c r="A81" s="6">
         <v>4</v>
       </c>
-      <c r="B81" s="18" t="s">
+      <c r="B81" s="12" t="s">
         <v>441</v>
       </c>
-      <c r="C81" s="19" t="s">
+      <c r="C81" s="13" t="s">
         <v>442</v>
       </c>
       <c r="D81" s="8" t="s">
@@ -5850,14 +4618,14 @@
         <v>271</v>
       </c>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A82" s="17">
+    <row r="82" spans="1:5" ht="37" x14ac:dyDescent="0.45">
+      <c r="A82" s="6">
         <v>65</v>
       </c>
-      <c r="B82" s="18" t="s">
+      <c r="B82" s="12" t="s">
         <v>443</v>
       </c>
-      <c r="C82" s="19" t="s">
+      <c r="C82" s="13" t="s">
         <v>444</v>
       </c>
       <c r="D82" s="8" t="s">
@@ -5867,14 +4635,14 @@
         <v>271</v>
       </c>
     </row>
-    <row r="83" spans="1:5" ht="36" x14ac:dyDescent="0.35">
-      <c r="A83" s="17">
+    <row r="83" spans="1:5" ht="37" x14ac:dyDescent="0.45">
+      <c r="A83" s="6">
         <v>90</v>
       </c>
-      <c r="B83" s="18" t="s">
+      <c r="B83" s="12" t="s">
         <v>445</v>
       </c>
-      <c r="C83" s="19" t="s">
+      <c r="C83" s="13" t="s">
         <v>446</v>
       </c>
       <c r="D83" s="8" t="s">
@@ -5884,14 +4652,14 @@
         <v>271</v>
       </c>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A84" s="17">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A84" s="6">
         <v>97</v>
       </c>
-      <c r="B84" s="18" t="s">
+      <c r="B84" s="12" t="s">
         <v>447</v>
       </c>
-      <c r="C84" s="19" t="s">
+      <c r="C84" s="13" t="s">
         <v>448</v>
       </c>
       <c r="D84" s="8" t="s">
@@ -5901,14 +4669,14 @@
         <v>271</v>
       </c>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A85" s="17">
+    <row r="85" spans="1:5" ht="37" x14ac:dyDescent="0.45">
+      <c r="A85" s="6">
         <v>71</v>
       </c>
-      <c r="B85" s="18" t="s">
+      <c r="B85" s="12" t="s">
         <v>449</v>
       </c>
-      <c r="C85" s="19" t="s">
+      <c r="C85" s="13" t="s">
         <v>450</v>
       </c>
       <c r="D85" s="8" t="s">
@@ -5918,14 +4686,14 @@
         <v>271</v>
       </c>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A86" s="17">
+    <row r="86" spans="1:5" ht="37" x14ac:dyDescent="0.45">
+      <c r="A86" s="6">
         <v>72</v>
       </c>
-      <c r="B86" s="18" t="s">
+      <c r="B86" s="12" t="s">
         <v>451</v>
       </c>
-      <c r="C86" s="19" t="s">
+      <c r="C86" s="13" t="s">
         <v>452</v>
       </c>
       <c r="D86" s="8" t="s">
@@ -5935,14 +4703,14 @@
         <v>271</v>
       </c>
     </row>
-    <row r="87" spans="1:5" ht="36" x14ac:dyDescent="0.35">
-      <c r="A87" s="17">
+    <row r="87" spans="1:5" ht="37" x14ac:dyDescent="0.45">
+      <c r="A87" s="6">
         <v>17</v>
       </c>
-      <c r="B87" s="18" t="s">
+      <c r="B87" s="12" t="s">
         <v>454</v>
       </c>
-      <c r="C87" s="19" t="s">
+      <c r="C87" s="13" t="s">
         <v>453</v>
       </c>
       <c r="D87" s="8" t="s">
@@ -5952,14 +4720,14 @@
         <v>271</v>
       </c>
     </row>
-    <row r="88" spans="1:5" ht="36" x14ac:dyDescent="0.35">
-      <c r="A88" s="17">
+    <row r="88" spans="1:5" ht="37" x14ac:dyDescent="0.45">
+      <c r="A88" s="6">
         <v>18</v>
       </c>
-      <c r="B88" s="18" t="s">
+      <c r="B88" s="12" t="s">
         <v>455</v>
       </c>
-      <c r="C88" s="19" t="s">
+      <c r="C88" s="13" t="s">
         <v>456</v>
       </c>
       <c r="D88" s="8" t="s">
@@ -5969,14 +4737,14 @@
         <v>271</v>
       </c>
     </row>
-    <row r="89" spans="1:5" ht="36" x14ac:dyDescent="0.35">
-      <c r="A89" s="17">
+    <row r="89" spans="1:5" ht="37" x14ac:dyDescent="0.45">
+      <c r="A89" s="6">
         <v>19</v>
       </c>
-      <c r="B89" s="18" t="s">
+      <c r="B89" s="12" t="s">
         <v>457</v>
       </c>
-      <c r="C89" s="19" t="s">
+      <c r="C89" s="13" t="s">
         <v>458</v>
       </c>
       <c r="D89" s="8" t="s">
@@ -5986,14 +4754,14 @@
         <v>271</v>
       </c>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A90" s="17">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A90" s="6">
         <v>38</v>
       </c>
-      <c r="B90" s="18" t="s">
+      <c r="B90" s="12" t="s">
         <v>459</v>
       </c>
-      <c r="C90" s="19" t="s">
+      <c r="C90" s="13" t="s">
         <v>460</v>
       </c>
       <c r="D90" s="8" t="s">
@@ -6003,14 +4771,14 @@
         <v>271</v>
       </c>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A91" s="17">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A91" s="6">
         <v>37</v>
       </c>
-      <c r="B91" s="18" t="s">
+      <c r="B91" s="12" t="s">
         <v>461</v>
       </c>
-      <c r="C91" s="19" t="s">
+      <c r="C91" s="13" t="s">
         <v>462</v>
       </c>
       <c r="D91" s="8" t="s">
@@ -6020,14 +4788,14 @@
         <v>271</v>
       </c>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A92" s="17">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A92" s="6">
         <v>29</v>
       </c>
-      <c r="B92" s="18" t="s">
+      <c r="B92" s="12" t="s">
         <v>463</v>
       </c>
-      <c r="C92" s="19" t="s">
+      <c r="C92" s="13" t="s">
         <v>464</v>
       </c>
       <c r="D92" s="8" t="s">
@@ -6037,14 +4805,14 @@
         <v>271</v>
       </c>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A93" s="17">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A93" s="6">
         <v>27</v>
       </c>
-      <c r="B93" s="18" t="s">
+      <c r="B93" s="12" t="s">
         <v>465</v>
       </c>
-      <c r="C93" s="19" t="s">
+      <c r="C93" s="13" t="s">
         <v>466</v>
       </c>
       <c r="D93" s="8" t="s">
@@ -6054,14 +4822,14 @@
         <v>271</v>
       </c>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A94" s="17">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A94" s="6">
         <v>28</v>
       </c>
-      <c r="B94" s="18" t="s">
+      <c r="B94" s="12" t="s">
         <v>467</v>
       </c>
-      <c r="C94" s="19" t="s">
+      <c r="C94" s="13" t="s">
         <v>468</v>
       </c>
       <c r="D94" s="8" t="s">
@@ -6071,14 +4839,14 @@
         <v>271</v>
       </c>
     </row>
-    <row r="95" spans="1:5" ht="36" x14ac:dyDescent="0.35">
-      <c r="A95" s="17">
+    <row r="95" spans="1:5" ht="37" x14ac:dyDescent="0.45">
+      <c r="A95" s="6">
         <v>52</v>
       </c>
-      <c r="B95" s="18" t="s">
+      <c r="B95" s="12" t="s">
         <v>469</v>
       </c>
-      <c r="C95" s="19" t="s">
+      <c r="C95" s="13" t="s">
         <v>470</v>
       </c>
       <c r="D95" s="8" t="s">
@@ -6088,14 +4856,14 @@
         <v>271</v>
       </c>
     </row>
-    <row r="96" spans="1:5" ht="36" x14ac:dyDescent="0.35">
-      <c r="A96" s="17">
+    <row r="96" spans="1:5" ht="37" x14ac:dyDescent="0.45">
+      <c r="A96" s="6">
         <v>53</v>
       </c>
-      <c r="B96" s="18" t="s">
+      <c r="B96" s="12" t="s">
         <v>471</v>
       </c>
-      <c r="C96" s="19" t="s">
+      <c r="C96" s="13" t="s">
         <v>472</v>
       </c>
       <c r="D96" s="8" t="s">
@@ -6105,14 +4873,14 @@
         <v>271</v>
       </c>
     </row>
-    <row r="97" spans="1:5" ht="36" x14ac:dyDescent="0.35">
-      <c r="A97" s="17">
+    <row r="97" spans="1:5" ht="37" x14ac:dyDescent="0.45">
+      <c r="A97" s="6">
         <v>51</v>
       </c>
-      <c r="B97" s="18" t="s">
+      <c r="B97" s="12" t="s">
         <v>473</v>
       </c>
-      <c r="C97" s="19" t="s">
+      <c r="C97" s="13" t="s">
         <v>474</v>
       </c>
       <c r="D97" s="8" t="s">
@@ -6122,14 +4890,14 @@
         <v>271</v>
       </c>
     </row>
-    <row r="98" spans="1:5" ht="36" x14ac:dyDescent="0.35">
-      <c r="A98" s="17">
+    <row r="98" spans="1:5" ht="37" x14ac:dyDescent="0.45">
+      <c r="A98" s="6">
         <v>50</v>
       </c>
-      <c r="B98" s="18" t="s">
+      <c r="B98" s="12" t="s">
         <v>475</v>
       </c>
-      <c r="C98" s="19" t="s">
+      <c r="C98" s="13" t="s">
         <v>476</v>
       </c>
       <c r="D98" s="8" t="s">
@@ -6139,14 +4907,14 @@
         <v>271</v>
       </c>
     </row>
-    <row r="99" spans="1:5" ht="36" x14ac:dyDescent="0.35">
-      <c r="A99" s="17">
+    <row r="99" spans="1:5" ht="37" x14ac:dyDescent="0.45">
+      <c r="A99" s="6">
         <v>54</v>
       </c>
-      <c r="B99" s="18" t="s">
+      <c r="B99" s="12" t="s">
         <v>477</v>
       </c>
-      <c r="C99" s="19" t="s">
+      <c r="C99" s="13" t="s">
         <v>478</v>
       </c>
       <c r="D99" s="8" t="s">
@@ -6156,14 +4924,14 @@
         <v>271</v>
       </c>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A100" s="17">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A100" s="6">
         <v>94</v>
       </c>
-      <c r="B100" s="18" t="s">
+      <c r="B100" s="12" t="s">
         <v>479</v>
       </c>
-      <c r="C100" s="19" t="s">
+      <c r="C100" s="13" t="s">
         <v>480</v>
       </c>
       <c r="D100" s="8" t="s">
@@ -6173,14 +4941,14 @@
         <v>271</v>
       </c>
     </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A101" s="17">
+    <row r="101" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A101" s="6">
         <v>87</v>
       </c>
-      <c r="B101" s="18" t="s">
+      <c r="B101" s="12" t="s">
         <v>481</v>
       </c>
-      <c r="C101" s="19" t="s">
+      <c r="C101" s="13" t="s">
         <v>482</v>
       </c>
       <c r="D101" s="8" t="s">
@@ -6190,14 +4958,14 @@
         <v>271</v>
       </c>
     </row>
-    <row r="102" spans="1:5" ht="36" x14ac:dyDescent="0.35">
-      <c r="A102" s="17">
+    <row r="102" spans="1:5" ht="37" x14ac:dyDescent="0.45">
+      <c r="A102" s="6">
         <v>12</v>
       </c>
-      <c r="B102" s="18" t="s">
+      <c r="B102" s="12" t="s">
         <v>483</v>
       </c>
-      <c r="C102" s="19" t="s">
+      <c r="C102" s="13" t="s">
         <v>484</v>
       </c>
       <c r="D102" s="8" t="s">
@@ -6207,14 +4975,14 @@
         <v>271</v>
       </c>
     </row>
-    <row r="103" spans="1:5" ht="36" x14ac:dyDescent="0.35">
-      <c r="A103" s="17">
+    <row r="103" spans="1:5" ht="37" x14ac:dyDescent="0.45">
+      <c r="A103" s="6">
         <v>85</v>
       </c>
-      <c r="B103" s="18" t="s">
+      <c r="B103" s="12" t="s">
         <v>485</v>
       </c>
-      <c r="C103" s="19" t="s">
+      <c r="C103" s="13" t="s">
         <v>486</v>
       </c>
       <c r="D103" s="8" t="s">
@@ -6224,14 +4992,14 @@
         <v>271</v>
       </c>
     </row>
-    <row r="104" spans="1:5" ht="36" x14ac:dyDescent="0.35">
-      <c r="A104" s="17">
+    <row r="104" spans="1:5" ht="37" x14ac:dyDescent="0.45">
+      <c r="A104" s="6">
         <v>11</v>
       </c>
-      <c r="B104" s="18" t="s">
+      <c r="B104" s="12" t="s">
         <v>487</v>
       </c>
-      <c r="C104" s="19" t="s">
+      <c r="C104" s="13" t="s">
         <v>488</v>
       </c>
       <c r="D104" s="8" t="s">
@@ -6241,14 +5009,14 @@
         <v>271</v>
       </c>
     </row>
-    <row r="105" spans="1:5" ht="36" x14ac:dyDescent="0.35">
-      <c r="A105" s="17">
+    <row r="105" spans="1:5" ht="37" x14ac:dyDescent="0.45">
+      <c r="A105" s="6">
         <v>13</v>
       </c>
-      <c r="B105" s="18" t="s">
+      <c r="B105" s="12" t="s">
         <v>489</v>
       </c>
-      <c r="C105" s="19" t="s">
+      <c r="C105" s="13" t="s">
         <v>490</v>
       </c>
       <c r="D105" s="8" t="s">
@@ -6258,14 +5026,14 @@
         <v>271</v>
       </c>
     </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A106" s="17">
+    <row r="106" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A106" s="6">
         <v>44</v>
       </c>
-      <c r="B106" s="18" t="s">
+      <c r="B106" s="12" t="s">
         <v>491</v>
       </c>
-      <c r="C106" s="19" t="s">
+      <c r="C106" s="13" t="s">
         <v>492</v>
       </c>
       <c r="D106" s="8" t="s">
@@ -6275,14 +5043,14 @@
         <v>271</v>
       </c>
     </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A107" s="17">
+    <row r="107" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A107" s="6">
         <v>90</v>
       </c>
-      <c r="B107" s="18" t="s">
+      <c r="B107" s="12" t="s">
         <v>493</v>
       </c>
-      <c r="C107" s="19" t="s">
+      <c r="C107" s="13" t="s">
         <v>494</v>
       </c>
       <c r="D107" s="8" t="s">
@@ -6292,14 +5060,14 @@
         <v>271</v>
       </c>
     </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A108" s="17">
+    <row r="108" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A108" s="6">
         <v>43</v>
       </c>
-      <c r="B108" s="18" t="s">
+      <c r="B108" s="12" t="s">
         <v>495</v>
       </c>
-      <c r="C108" s="19" t="s">
+      <c r="C108" s="13" t="s">
         <v>496</v>
       </c>
       <c r="D108" s="8" t="s">
@@ -6309,14 +5077,14 @@
         <v>271</v>
       </c>
     </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A109" s="17">
+    <row r="109" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A109" s="6">
         <v>92</v>
       </c>
-      <c r="B109" s="18" t="s">
+      <c r="B109" s="12" t="s">
         <v>497</v>
       </c>
-      <c r="C109" s="19" t="s">
+      <c r="C109" s="13" t="s">
         <v>498</v>
       </c>
       <c r="D109" s="8" t="s">
@@ -6326,14 +5094,14 @@
         <v>271</v>
       </c>
     </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A110" s="17">
+    <row r="110" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A110" s="6">
         <v>93</v>
       </c>
-      <c r="B110" s="18" t="s">
+      <c r="B110" s="12" t="s">
         <v>499</v>
       </c>
-      <c r="C110" s="19" t="s">
+      <c r="C110" s="13" t="s">
         <v>500</v>
       </c>
       <c r="D110" s="8" t="s">
@@ -6343,14 +5111,14 @@
         <v>271</v>
       </c>
     </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A111" s="17">
+    <row r="111" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A111" s="6">
         <v>39</v>
       </c>
-      <c r="B111" s="18" t="s">
+      <c r="B111" s="12" t="s">
         <v>501</v>
       </c>
-      <c r="C111" s="19" t="s">
+      <c r="C111" s="13" t="s">
         <v>502</v>
       </c>
       <c r="D111" s="8" t="s">
@@ -6360,14 +5128,14 @@
         <v>271</v>
       </c>
     </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A112" s="17">
+    <row r="112" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A112" s="6">
         <v>45</v>
       </c>
-      <c r="B112" s="18" t="s">
+      <c r="B112" s="12" t="s">
         <v>333</v>
       </c>
-      <c r="C112" s="19" t="s">
+      <c r="C112" s="13" t="s">
         <v>334</v>
       </c>
       <c r="D112" s="8" t="s">
@@ -6377,14 +5145,14 @@
         <v>271</v>
       </c>
     </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A113" s="17">
+    <row r="113" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A113" s="6">
         <v>26</v>
       </c>
-      <c r="B113" s="18" t="s">
+      <c r="B113" s="12" t="s">
         <v>503</v>
       </c>
-      <c r="C113" s="19" t="s">
+      <c r="C113" s="13" t="s">
         <v>504</v>
       </c>
       <c r="D113" s="8" t="s">
@@ -6394,14 +5162,14 @@
         <v>271</v>
       </c>
     </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A114" s="17">
+    <row r="114" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A114" s="6">
         <v>25</v>
       </c>
-      <c r="B114" s="18" t="s">
+      <c r="B114" s="12" t="s">
         <v>505</v>
       </c>
-      <c r="C114" s="19" t="s">
+      <c r="C114" s="13" t="s">
         <v>506</v>
       </c>
       <c r="D114" s="8" t="s">
@@ -6411,14 +5179,14 @@
         <v>271</v>
       </c>
     </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A115" s="17">
+    <row r="115" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A115" s="6">
         <v>38</v>
       </c>
-      <c r="B115" s="18" t="s">
+      <c r="B115" s="12" t="s">
         <v>507</v>
       </c>
-      <c r="C115" s="19" t="s">
+      <c r="C115" s="13" t="s">
         <v>508</v>
       </c>
       <c r="D115" s="8" t="s">
@@ -6428,14 +5196,14 @@
         <v>271</v>
       </c>
     </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A116" s="17">
+    <row r="116" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A116" s="6">
         <v>22</v>
       </c>
-      <c r="B116" s="18" t="s">
+      <c r="B116" s="12" t="s">
         <v>509</v>
       </c>
-      <c r="C116" s="19" t="s">
+      <c r="C116" s="13" t="s">
         <v>510</v>
       </c>
       <c r="D116" s="8" t="s">
@@ -6445,14 +5213,14 @@
         <v>271</v>
       </c>
     </row>
-    <row r="117" spans="1:5" ht="36" x14ac:dyDescent="0.35">
-      <c r="A117" s="17">
+    <row r="117" spans="1:5" ht="37" x14ac:dyDescent="0.45">
+      <c r="A117" s="6">
         <v>30</v>
       </c>
-      <c r="B117" s="18" t="s">
+      <c r="B117" s="12" t="s">
         <v>511</v>
       </c>
-      <c r="C117" s="19" t="s">
+      <c r="C117" s="13" t="s">
         <v>512</v>
       </c>
       <c r="D117" s="8" t="s">
@@ -6462,14 +5230,14 @@
         <v>271</v>
       </c>
     </row>
-    <row r="118" spans="1:5" ht="36" x14ac:dyDescent="0.35">
-      <c r="A118" s="17">
+    <row r="118" spans="1:5" ht="37" x14ac:dyDescent="0.45">
+      <c r="A118" s="6">
         <v>49</v>
       </c>
-      <c r="B118" s="18" t="s">
+      <c r="B118" s="12" t="s">
         <v>513</v>
       </c>
-      <c r="C118" s="19" t="s">
+      <c r="C118" s="13" t="s">
         <v>514</v>
       </c>
       <c r="D118" s="8" t="s">
@@ -6479,14 +5247,14 @@
         <v>271</v>
       </c>
     </row>
-    <row r="119" spans="1:5" ht="36" x14ac:dyDescent="0.35">
-      <c r="A119" s="17">
+    <row r="119" spans="1:5" ht="37" x14ac:dyDescent="0.45">
+      <c r="A119" s="6">
         <v>48</v>
       </c>
-      <c r="B119" s="18" t="s">
+      <c r="B119" s="12" t="s">
         <v>515</v>
       </c>
-      <c r="C119" s="19" t="s">
+      <c r="C119" s="13" t="s">
         <v>516</v>
       </c>
       <c r="D119" s="8" t="s">
@@ -6496,14 +5264,14 @@
         <v>271</v>
       </c>
     </row>
-    <row r="120" spans="1:5" ht="36" x14ac:dyDescent="0.35">
-      <c r="A120" s="17">
+    <row r="120" spans="1:5" ht="37" x14ac:dyDescent="0.45">
+      <c r="A120" s="6">
         <v>36</v>
       </c>
-      <c r="B120" s="18" t="s">
+      <c r="B120" s="12" t="s">
         <v>517</v>
       </c>
-      <c r="C120" s="19" t="s">
+      <c r="C120" s="13" t="s">
         <v>518</v>
       </c>
       <c r="D120" s="8" t="s">
@@ -6513,14 +5281,14 @@
         <v>271</v>
       </c>
     </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A121" s="17">
+    <row r="121" spans="1:5" ht="37" x14ac:dyDescent="0.45">
+      <c r="A121" s="6">
         <v>74</v>
       </c>
-      <c r="B121" s="18" t="s">
+      <c r="B121" s="12" t="s">
         <v>519</v>
       </c>
-      <c r="C121" s="19" t="s">
+      <c r="C121" s="13" t="s">
         <v>520</v>
       </c>
       <c r="D121" s="8" t="s">
@@ -6530,14 +5298,14 @@
         <v>271</v>
       </c>
     </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A122" s="17">
+    <row r="122" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A122" s="6">
         <v>37</v>
       </c>
-      <c r="B122" s="18" t="s">
+      <c r="B122" s="12" t="s">
         <v>521</v>
       </c>
-      <c r="C122" s="19" t="s">
+      <c r="C122" s="13" t="s">
         <v>522</v>
       </c>
       <c r="D122" s="8" t="s">
@@ -6547,14 +5315,14 @@
         <v>271</v>
       </c>
     </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A123" s="17">
+    <row r="123" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A123" s="6">
         <v>23</v>
       </c>
-      <c r="B123" s="18" t="s">
+      <c r="B123" s="12" t="s">
         <v>523</v>
       </c>
-      <c r="C123" s="19" t="s">
+      <c r="C123" s="13" t="s">
         <v>524</v>
       </c>
       <c r="D123" s="8" t="s">
@@ -6564,14 +5332,14 @@
         <v>271</v>
       </c>
     </row>
-    <row r="124" spans="1:5" ht="36" x14ac:dyDescent="0.35">
-      <c r="A124" s="17">
+    <row r="124" spans="1:5" ht="37" x14ac:dyDescent="0.45">
+      <c r="A124" s="6">
         <v>91</v>
       </c>
-      <c r="B124" s="18" t="s">
+      <c r="B124" s="12" t="s">
         <v>525</v>
       </c>
-      <c r="C124" s="19" t="s">
+      <c r="C124" s="13" t="s">
         <v>526</v>
       </c>
       <c r="D124" s="8" t="s">
@@ -6581,14 +5349,14 @@
         <v>271</v>
       </c>
     </row>
-    <row r="125" spans="1:5" ht="36" x14ac:dyDescent="0.35">
-      <c r="A125" s="17">
+    <row r="125" spans="1:5" ht="37" x14ac:dyDescent="0.45">
+      <c r="A125" s="6">
         <v>89</v>
       </c>
-      <c r="B125" s="18" t="s">
+      <c r="B125" s="12" t="s">
         <v>527</v>
       </c>
-      <c r="C125" s="19" t="s">
+      <c r="C125" s="13" t="s">
         <v>528</v>
       </c>
       <c r="D125" s="8" t="s">
@@ -6598,14 +5366,14 @@
         <v>271</v>
       </c>
     </row>
-    <row r="126" spans="1:5" ht="36" x14ac:dyDescent="0.35">
-      <c r="A126" s="17">
+    <row r="126" spans="1:5" ht="37" x14ac:dyDescent="0.45">
+      <c r="A126" s="6">
         <v>80</v>
       </c>
-      <c r="B126" s="18" t="s">
+      <c r="B126" s="12" t="s">
         <v>529</v>
       </c>
-      <c r="C126" s="19" t="s">
+      <c r="C126" s="13" t="s">
         <v>530</v>
       </c>
       <c r="D126" s="8" t="s">
@@ -6615,14 +5383,14 @@
         <v>271</v>
       </c>
     </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A127" s="17">
+    <row r="127" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A127" s="6">
         <v>12</v>
       </c>
-      <c r="B127" s="18" t="s">
+      <c r="B127" s="12" t="s">
         <v>531</v>
       </c>
-      <c r="C127" s="19" t="s">
+      <c r="C127" s="13" t="s">
         <v>532</v>
       </c>
       <c r="D127" s="8" t="s">
@@ -6632,14 +5400,14 @@
         <v>271</v>
       </c>
     </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A128" s="17">
+    <row r="128" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A128" s="6">
         <v>15</v>
       </c>
-      <c r="B128" s="18" t="s">
+      <c r="B128" s="12" t="s">
         <v>533</v>
       </c>
-      <c r="C128" s="19" t="s">
+      <c r="C128" s="13" t="s">
         <v>534</v>
       </c>
       <c r="D128" s="8" t="s">
@@ -6649,14 +5417,14 @@
         <v>271</v>
       </c>
     </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A129" s="17">
+    <row r="129" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A129" s="6">
         <v>13</v>
       </c>
-      <c r="B129" s="18" t="s">
+      <c r="B129" s="12" t="s">
         <v>535</v>
       </c>
-      <c r="C129" s="19" t="s">
+      <c r="C129" s="13" t="s">
         <v>536</v>
       </c>
       <c r="D129" s="8" t="s">
@@ -6666,14 +5434,14 @@
         <v>271</v>
       </c>
     </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A130" s="17">
+    <row r="130" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A130" s="6">
         <v>28</v>
       </c>
-      <c r="B130" s="18" t="s">
+      <c r="B130" s="12" t="s">
         <v>537</v>
       </c>
-      <c r="C130" s="19" t="s">
+      <c r="C130" s="13" t="s">
         <v>538</v>
       </c>
       <c r="D130" s="8" t="s">
@@ -6683,14 +5451,14 @@
         <v>271</v>
       </c>
     </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A131" s="17">
+    <row r="131" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A131" s="6">
         <v>10</v>
       </c>
-      <c r="B131" s="18" t="s">
+      <c r="B131" s="12" t="s">
         <v>539</v>
       </c>
-      <c r="C131" s="19" t="s">
+      <c r="C131" s="13" t="s">
         <v>540</v>
       </c>
       <c r="D131" s="8" t="s">
@@ -6700,14 +5468,14 @@
         <v>271</v>
       </c>
     </row>
-    <row r="132" spans="1:5" ht="36" x14ac:dyDescent="0.35">
-      <c r="A132" s="17">
+    <row r="132" spans="1:5" ht="37" x14ac:dyDescent="0.45">
+      <c r="A132" s="6">
         <v>81</v>
       </c>
-      <c r="B132" s="18" t="s">
+      <c r="B132" s="12" t="s">
         <v>541</v>
       </c>
-      <c r="C132" s="19" t="s">
+      <c r="C132" s="13" t="s">
         <v>542</v>
       </c>
       <c r="D132" s="8" t="s">
@@ -6717,14 +5485,14 @@
         <v>271</v>
       </c>
     </row>
-    <row r="133" spans="1:5" ht="36" x14ac:dyDescent="0.35">
-      <c r="A133" s="17">
+    <row r="133" spans="1:5" ht="37" x14ac:dyDescent="0.45">
+      <c r="A133" s="6">
         <v>25</v>
       </c>
-      <c r="B133" s="26" t="s">
+      <c r="B133" s="17" t="s">
         <v>552</v>
       </c>
-      <c r="C133" s="19" t="s">
+      <c r="C133" s="13" t="s">
         <v>553</v>
       </c>
       <c r="D133" s="8" t="s">
@@ -6734,14 +5502,14 @@
         <v>543</v>
       </c>
     </row>
-    <row r="134" spans="1:5" ht="36" x14ac:dyDescent="0.35">
-      <c r="A134" s="17">
+    <row r="134" spans="1:5" ht="37" x14ac:dyDescent="0.45">
+      <c r="A134" s="6">
         <v>35</v>
       </c>
-      <c r="B134" s="18" t="s">
+      <c r="B134" s="12" t="s">
         <v>554</v>
       </c>
-      <c r="C134" s="19" t="s">
+      <c r="C134" s="13" t="s">
         <v>555</v>
       </c>
       <c r="D134" s="8" t="s">
@@ -6751,14 +5519,14 @@
         <v>543</v>
       </c>
     </row>
-    <row r="135" spans="1:5" ht="36" x14ac:dyDescent="0.35">
-      <c r="A135" s="17">
+    <row r="135" spans="1:5" ht="37" x14ac:dyDescent="0.45">
+      <c r="A135" s="6">
         <v>22</v>
       </c>
-      <c r="B135" s="18" t="s">
+      <c r="B135" s="12" t="s">
         <v>556</v>
       </c>
-      <c r="C135" s="19" t="s">
+      <c r="C135" s="13" t="s">
         <v>557</v>
       </c>
       <c r="D135" s="8" t="s">
@@ -6768,14 +5536,14 @@
         <v>543</v>
       </c>
     </row>
-    <row r="136" spans="1:5" ht="36" x14ac:dyDescent="0.35">
-      <c r="A136" s="17">
+    <row r="136" spans="1:5" ht="37" x14ac:dyDescent="0.45">
+      <c r="A136" s="6">
         <v>21</v>
       </c>
-      <c r="B136" s="18" t="s">
+      <c r="B136" s="12" t="s">
         <v>558</v>
       </c>
-      <c r="C136" s="19" t="s">
+      <c r="C136" s="13" t="s">
         <v>559</v>
       </c>
       <c r="D136" s="8" t="s">
@@ -6785,14 +5553,14 @@
         <v>543</v>
       </c>
     </row>
-    <row r="137" spans="1:5" ht="36" x14ac:dyDescent="0.35">
-      <c r="A137" s="17">
+    <row r="137" spans="1:5" ht="37" x14ac:dyDescent="0.45">
+      <c r="A137" s="6">
         <v>20</v>
       </c>
-      <c r="B137" s="18" t="s">
+      <c r="B137" s="12" t="s">
         <v>560</v>
       </c>
-      <c r="C137" s="19" t="s">
+      <c r="C137" s="13" t="s">
         <v>561</v>
       </c>
       <c r="D137" s="8" t="s">
@@ -6802,14 +5570,14 @@
         <v>543</v>
       </c>
     </row>
-    <row r="138" spans="1:5" ht="36" x14ac:dyDescent="0.35">
-      <c r="A138" s="17">
+    <row r="138" spans="1:5" ht="37" x14ac:dyDescent="0.45">
+      <c r="A138" s="6">
         <v>23</v>
       </c>
-      <c r="B138" s="18" t="s">
+      <c r="B138" s="12" t="s">
         <v>562</v>
       </c>
-      <c r="C138" s="19" t="s">
+      <c r="C138" s="13" t="s">
         <v>563</v>
       </c>
       <c r="D138" s="8" t="s">
@@ -6819,14 +5587,14 @@
         <v>543</v>
       </c>
     </row>
-    <row r="139" spans="1:5" ht="36" x14ac:dyDescent="0.35">
-      <c r="A139" s="17">
+    <row r="139" spans="1:5" ht="37" x14ac:dyDescent="0.45">
+      <c r="A139" s="6">
         <v>24</v>
       </c>
-      <c r="B139" s="18" t="s">
+      <c r="B139" s="12" t="s">
         <v>564</v>
       </c>
-      <c r="C139" s="19" t="s">
+      <c r="C139" s="13" t="s">
         <v>565</v>
       </c>
       <c r="D139" s="8" t="s">
@@ -6836,14 +5604,14 @@
         <v>543</v>
       </c>
     </row>
-    <row r="140" spans="1:5" ht="36" x14ac:dyDescent="0.35">
-      <c r="A140" s="17">
+    <row r="140" spans="1:5" ht="37" x14ac:dyDescent="0.45">
+      <c r="A140" s="6">
         <v>40</v>
       </c>
-      <c r="B140" s="18" t="s">
+      <c r="B140" s="12" t="s">
         <v>575</v>
       </c>
-      <c r="C140" s="19" t="s">
+      <c r="C140" s="13" t="s">
         <v>576</v>
       </c>
       <c r="D140" s="8" t="s">
@@ -6853,14 +5621,14 @@
         <v>543</v>
       </c>
     </row>
-    <row r="141" spans="1:5" ht="36" x14ac:dyDescent="0.35">
-      <c r="A141" s="17">
+    <row r="141" spans="1:5" ht="37" x14ac:dyDescent="0.45">
+      <c r="A141" s="6">
         <v>70</v>
       </c>
-      <c r="B141" s="18" t="s">
+      <c r="B141" s="12" t="s">
         <v>577</v>
       </c>
-      <c r="C141" s="19" t="s">
+      <c r="C141" s="13" t="s">
         <v>578</v>
       </c>
       <c r="D141" s="8" t="s">
@@ -6870,14 +5638,14 @@
         <v>543</v>
       </c>
     </row>
-    <row r="142" spans="1:5" ht="36" x14ac:dyDescent="0.35">
-      <c r="A142" s="17">
+    <row r="142" spans="1:5" ht="37" x14ac:dyDescent="0.45">
+      <c r="A142" s="6">
         <v>73</v>
       </c>
-      <c r="B142" s="18" t="s">
+      <c r="B142" s="12" t="s">
         <v>579</v>
       </c>
-      <c r="C142" s="19" t="s">
+      <c r="C142" s="13" t="s">
         <v>580</v>
       </c>
       <c r="D142" s="8" t="s">
@@ -6887,14 +5655,14 @@
         <v>543</v>
       </c>
     </row>
-    <row r="143" spans="1:5" ht="36" x14ac:dyDescent="0.35">
-      <c r="A143" s="17">
+    <row r="143" spans="1:5" ht="37" x14ac:dyDescent="0.45">
+      <c r="A143" s="6">
         <v>71</v>
       </c>
-      <c r="B143" s="18" t="s">
+      <c r="B143" s="12" t="s">
         <v>581</v>
       </c>
-      <c r="C143" s="19" t="s">
+      <c r="C143" s="13" t="s">
         <v>582</v>
       </c>
       <c r="D143" s="8" t="s">
@@ -6904,14 +5672,14 @@
         <v>543</v>
       </c>
     </row>
-    <row r="144" spans="1:5" ht="36" x14ac:dyDescent="0.35">
-      <c r="A144" s="17">
+    <row r="144" spans="1:5" ht="37" x14ac:dyDescent="0.45">
+      <c r="A144" s="6">
         <v>31</v>
       </c>
-      <c r="B144" s="18" t="s">
+      <c r="B144" s="12" t="s">
         <v>587</v>
       </c>
-      <c r="C144" s="19" t="s">
+      <c r="C144" s="13" t="s">
         <v>588</v>
       </c>
       <c r="D144" s="8" t="s">
@@ -6921,14 +5689,14 @@
         <v>543</v>
       </c>
     </row>
-    <row r="145" spans="1:5" ht="36" x14ac:dyDescent="0.35">
-      <c r="A145" s="17">
+    <row r="145" spans="1:5" ht="37" x14ac:dyDescent="0.45">
+      <c r="A145" s="6">
         <v>30</v>
       </c>
-      <c r="B145" s="18" t="s">
+      <c r="B145" s="12" t="s">
         <v>589</v>
       </c>
-      <c r="C145" s="19" t="s">
+      <c r="C145" s="13" t="s">
         <v>590</v>
       </c>
       <c r="D145" s="8" t="s">
@@ -6938,14 +5706,14 @@
         <v>543</v>
       </c>
     </row>
-    <row r="146" spans="1:5" ht="36" x14ac:dyDescent="0.35">
-      <c r="A146" s="17">
+    <row r="146" spans="1:5" ht="37" x14ac:dyDescent="0.45">
+      <c r="A146" s="6">
         <v>6</v>
       </c>
-      <c r="B146" s="18" t="s">
+      <c r="B146" s="12" t="s">
         <v>593</v>
       </c>
-      <c r="C146" s="19" t="s">
+      <c r="C146" s="13" t="s">
         <v>594</v>
       </c>
       <c r="D146" s="8" t="s">
@@ -6955,14 +5723,14 @@
         <v>543</v>
       </c>
     </row>
-    <row r="147" spans="1:5" ht="36" x14ac:dyDescent="0.35">
-      <c r="A147" s="17">
+    <row r="147" spans="1:5" ht="37" x14ac:dyDescent="0.45">
+      <c r="A147" s="6">
         <v>1</v>
       </c>
-      <c r="B147" s="18" t="s">
+      <c r="B147" s="12" t="s">
         <v>595</v>
       </c>
-      <c r="C147" s="19" t="s">
+      <c r="C147" s="13" t="s">
         <v>596</v>
       </c>
       <c r="D147" s="8" t="s">
@@ -6972,14 +5740,14 @@
         <v>543</v>
       </c>
     </row>
-    <row r="148" spans="1:5" ht="36" x14ac:dyDescent="0.35">
-      <c r="A148" s="17">
+    <row r="148" spans="1:5" ht="37" x14ac:dyDescent="0.45">
+      <c r="A148" s="6">
         <v>2</v>
       </c>
-      <c r="B148" s="18" t="s">
+      <c r="B148" s="12" t="s">
         <v>597</v>
       </c>
-      <c r="C148" s="19" t="s">
+      <c r="C148" s="13" t="s">
         <v>598</v>
       </c>
       <c r="D148" s="8" t="s">
@@ -6989,14 +5757,14 @@
         <v>543</v>
       </c>
     </row>
-    <row r="149" spans="1:5" ht="36" x14ac:dyDescent="0.35">
-      <c r="A149" s="17">
+    <row r="149" spans="1:5" ht="37" x14ac:dyDescent="0.45">
+      <c r="A149" s="6">
         <v>3</v>
       </c>
-      <c r="B149" s="18" t="s">
+      <c r="B149" s="12" t="s">
         <v>599</v>
       </c>
-      <c r="C149" s="19" t="s">
+      <c r="C149" s="13" t="s">
         <v>600</v>
       </c>
       <c r="D149" s="8" t="s">
@@ -7006,14 +5774,14 @@
         <v>543</v>
       </c>
     </row>
-    <row r="150" spans="1:5" ht="36" x14ac:dyDescent="0.35">
-      <c r="A150" s="17">
+    <row r="150" spans="1:5" ht="37" x14ac:dyDescent="0.45">
+      <c r="A150" s="6">
         <v>7</v>
       </c>
-      <c r="B150" s="18" t="s">
+      <c r="B150" s="12" t="s">
         <v>601</v>
       </c>
-      <c r="C150" s="19" t="s">
+      <c r="C150" s="13" t="s">
         <v>602</v>
       </c>
       <c r="D150" s="8" t="s">
@@ -7023,14 +5791,14 @@
         <v>543</v>
       </c>
     </row>
-    <row r="151" spans="1:5" ht="36" x14ac:dyDescent="0.35">
-      <c r="A151" s="17">
+    <row r="151" spans="1:5" ht="37" x14ac:dyDescent="0.45">
+      <c r="A151" s="6">
         <v>4</v>
       </c>
-      <c r="B151" s="18" t="s">
+      <c r="B151" s="12" t="s">
         <v>603</v>
       </c>
-      <c r="C151" s="19" t="s">
+      <c r="C151" s="13" t="s">
         <v>604</v>
       </c>
       <c r="D151" s="8" t="s">
@@ -7040,14 +5808,14 @@
         <v>543</v>
       </c>
     </row>
-    <row r="152" spans="1:5" ht="36" x14ac:dyDescent="0.35">
-      <c r="A152" s="17">
+    <row r="152" spans="1:5" ht="37" x14ac:dyDescent="0.45">
+      <c r="A152" s="6">
         <v>5</v>
       </c>
-      <c r="B152" s="18" t="s">
+      <c r="B152" s="12" t="s">
         <v>605</v>
       </c>
-      <c r="C152" s="19" t="s">
+      <c r="C152" s="13" t="s">
         <v>606</v>
       </c>
       <c r="D152" s="8" t="s">
@@ -7057,14 +5825,14 @@
         <v>543</v>
       </c>
     </row>
-    <row r="153" spans="1:5" ht="36" x14ac:dyDescent="0.35">
-      <c r="A153" s="17">
+    <row r="153" spans="1:5" ht="37" x14ac:dyDescent="0.45">
+      <c r="A153" s="6">
         <v>75</v>
       </c>
-      <c r="B153" s="18" t="s">
+      <c r="B153" s="12" t="s">
         <v>607</v>
       </c>
-      <c r="C153" s="19" t="s">
+      <c r="C153" s="13" t="s">
         <v>608</v>
       </c>
       <c r="D153" s="8" t="s">
@@ -7074,14 +5842,14 @@
         <v>543</v>
       </c>
     </row>
-    <row r="154" spans="1:5" ht="36" x14ac:dyDescent="0.35">
-      <c r="A154" s="17">
+    <row r="154" spans="1:5" ht="37" x14ac:dyDescent="0.45">
+      <c r="A154" s="6">
         <v>74</v>
       </c>
-      <c r="B154" s="18" t="s">
+      <c r="B154" s="12" t="s">
         <v>609</v>
       </c>
-      <c r="C154" s="19" t="s">
+      <c r="C154" s="13" t="s">
         <v>610</v>
       </c>
       <c r="D154" s="8" t="s">
@@ -7091,14 +5859,14 @@
         <v>543</v>
       </c>
     </row>
-    <row r="155" spans="1:5" ht="36" x14ac:dyDescent="0.35">
-      <c r="A155" s="17">
+    <row r="155" spans="1:5" ht="37" x14ac:dyDescent="0.45">
+      <c r="A155" s="6">
         <v>36</v>
       </c>
-      <c r="B155" s="18" t="s">
+      <c r="B155" s="12" t="s">
         <v>335</v>
       </c>
-      <c r="C155" s="19" t="s">
+      <c r="C155" s="13" t="s">
         <v>611</v>
       </c>
       <c r="D155" s="8" t="s">
@@ -7108,15 +5876,15 @@
         <v>543</v>
       </c>
     </row>
-    <row r="156" spans="1:5" ht="36" x14ac:dyDescent="0.35">
-      <c r="A156" s="17">
+    <row r="156" spans="1:5" ht="37" x14ac:dyDescent="0.45">
+      <c r="A156" s="6">
         <v>76</v>
       </c>
-      <c r="B156" s="13" t="s">
-        <v>673</v>
-      </c>
-      <c r="C156" s="13" t="s">
-        <v>674</v>
+      <c r="B156" t="s">
+        <v>671</v>
+      </c>
+      <c r="C156" t="s">
+        <v>672</v>
       </c>
       <c r="D156" s="8" t="s">
         <v>547</v>
@@ -7125,14 +5893,14 @@
         <v>543</v>
       </c>
     </row>
-    <row r="157" spans="1:5" ht="36" x14ac:dyDescent="0.35">
-      <c r="A157" s="17">
+    <row r="157" spans="1:5" ht="37" x14ac:dyDescent="0.45">
+      <c r="A157" s="6">
         <v>84</v>
       </c>
-      <c r="B157" s="18" t="s">
+      <c r="B157" s="12" t="s">
         <v>632</v>
       </c>
-      <c r="C157" s="19" t="s">
+      <c r="C157" s="13" t="s">
         <v>633</v>
       </c>
       <c r="D157" s="8" t="s">
@@ -7142,14 +5910,14 @@
         <v>543</v>
       </c>
     </row>
-    <row r="158" spans="1:5" ht="36" x14ac:dyDescent="0.35">
-      <c r="A158" s="17">
+    <row r="158" spans="1:5" ht="37" x14ac:dyDescent="0.45">
+      <c r="A158" s="6">
         <v>86</v>
       </c>
-      <c r="B158" s="18" t="s">
+      <c r="B158" s="12" t="s">
         <v>634</v>
       </c>
-      <c r="C158" s="19" t="s">
+      <c r="C158" s="13" t="s">
         <v>635</v>
       </c>
       <c r="D158" s="8" t="s">
@@ -7159,14 +5927,14 @@
         <v>543</v>
       </c>
     </row>
-    <row r="159" spans="1:5" ht="36" x14ac:dyDescent="0.35">
-      <c r="A159" s="17">
+    <row r="159" spans="1:5" ht="37" x14ac:dyDescent="0.45">
+      <c r="A159" s="6">
         <v>85</v>
       </c>
-      <c r="B159" s="18" t="s">
+      <c r="B159" s="12" t="s">
         <v>636</v>
       </c>
-      <c r="C159" s="19" t="s">
+      <c r="C159" s="13" t="s">
         <v>637</v>
       </c>
       <c r="D159" s="8" t="s">
@@ -7176,14 +5944,14 @@
         <v>543</v>
       </c>
     </row>
-    <row r="160" spans="1:5" ht="36" x14ac:dyDescent="0.35">
-      <c r="A160" s="17">
+    <row r="160" spans="1:5" ht="37" x14ac:dyDescent="0.45">
+      <c r="A160" s="6">
         <v>87</v>
       </c>
-      <c r="B160" s="18" t="s">
+      <c r="B160" s="12" t="s">
         <v>638</v>
       </c>
-      <c r="C160" s="19" t="s">
+      <c r="C160" s="13" t="s">
         <v>639</v>
       </c>
       <c r="D160" s="8" t="s">
@@ -7193,14 +5961,14 @@
         <v>543</v>
       </c>
     </row>
-    <row r="161" spans="1:5" ht="36" x14ac:dyDescent="0.35">
-      <c r="A161" s="17">
+    <row r="161" spans="1:5" ht="37" x14ac:dyDescent="0.45">
+      <c r="A161" s="6">
         <v>80</v>
       </c>
-      <c r="B161" s="18" t="s">
+      <c r="B161" s="12" t="s">
         <v>640</v>
       </c>
-      <c r="C161" s="19" t="s">
+      <c r="C161" s="13" t="s">
         <v>641</v>
       </c>
       <c r="D161" s="8" t="s">
@@ -7210,14 +5978,14 @@
         <v>543</v>
       </c>
     </row>
-    <row r="162" spans="1:5" ht="36" x14ac:dyDescent="0.35">
-      <c r="A162" s="17">
+    <row r="162" spans="1:5" ht="37" x14ac:dyDescent="0.45">
+      <c r="A162" s="6">
         <v>81</v>
       </c>
-      <c r="B162" s="18" t="s">
+      <c r="B162" s="12" t="s">
         <v>642</v>
       </c>
-      <c r="C162" s="19" t="s">
+      <c r="C162" s="13" t="s">
         <v>643</v>
       </c>
       <c r="D162" s="8" t="s">
@@ -7227,14 +5995,14 @@
         <v>543</v>
       </c>
     </row>
-    <row r="163" spans="1:5" ht="36" x14ac:dyDescent="0.35">
-      <c r="A163" s="17">
+    <row r="163" spans="1:5" ht="37" x14ac:dyDescent="0.45">
+      <c r="A163" s="6">
         <v>82</v>
       </c>
-      <c r="B163" s="18" t="s">
+      <c r="B163" s="12" t="s">
         <v>644</v>
       </c>
-      <c r="C163" s="19" t="s">
+      <c r="C163" s="13" t="s">
         <v>645</v>
       </c>
       <c r="D163" s="8" t="s">
@@ -7244,14 +6012,14 @@
         <v>543</v>
       </c>
     </row>
-    <row r="164" spans="1:5" ht="36" x14ac:dyDescent="0.35">
-      <c r="A164" s="17">
+    <row r="164" spans="1:5" ht="37" x14ac:dyDescent="0.45">
+      <c r="A164" s="6">
         <v>83</v>
       </c>
-      <c r="B164" s="18" t="s">
+      <c r="B164" s="12" t="s">
         <v>646</v>
       </c>
-      <c r="C164" s="19" t="s">
+      <c r="C164" s="13" t="s">
         <v>647</v>
       </c>
       <c r="D164" s="8" t="s">
@@ -7261,14 +6029,14 @@
         <v>543</v>
       </c>
     </row>
-    <row r="165" spans="1:5" ht="36" x14ac:dyDescent="0.35">
-      <c r="A165" s="17">
+    <row r="165" spans="1:5" ht="37" x14ac:dyDescent="0.45">
+      <c r="A165" s="6">
         <v>37</v>
       </c>
-      <c r="B165" s="18" t="s">
+      <c r="B165" s="12" t="s">
         <v>648</v>
       </c>
-      <c r="C165" s="19" t="s">
+      <c r="C165" s="13" t="s">
         <v>649</v>
       </c>
       <c r="D165" s="8" t="s">
@@ -7278,14 +6046,14 @@
         <v>543</v>
       </c>
     </row>
-    <row r="166" spans="1:5" ht="36" x14ac:dyDescent="0.35">
-      <c r="A166" s="17">
+    <row r="166" spans="1:5" ht="37" x14ac:dyDescent="0.45">
+      <c r="A166" s="6">
         <v>32</v>
       </c>
-      <c r="B166" s="18" t="s">
+      <c r="B166" s="12" t="s">
         <v>650</v>
       </c>
-      <c r="C166" s="19" t="s">
+      <c r="C166" s="13" t="s">
         <v>651</v>
       </c>
       <c r="D166" s="8" t="s">
@@ -7295,14 +6063,14 @@
         <v>543</v>
       </c>
     </row>
-    <row r="167" spans="1:5" ht="36" x14ac:dyDescent="0.35">
-      <c r="A167" s="17">
+    <row r="167" spans="1:5" ht="37" x14ac:dyDescent="0.45">
+      <c r="A167" s="6">
         <v>33</v>
       </c>
-      <c r="B167" s="18" t="s">
+      <c r="B167" s="12" t="s">
         <v>652</v>
       </c>
-      <c r="C167" s="19" t="s">
+      <c r="C167" s="13" t="s">
         <v>653</v>
       </c>
       <c r="D167" s="8" t="s">
@@ -7312,14 +6080,14 @@
         <v>543</v>
       </c>
     </row>
-    <row r="168" spans="1:5" ht="36" x14ac:dyDescent="0.35">
-      <c r="A168" s="17">
+    <row r="168" spans="1:5" ht="37" x14ac:dyDescent="0.45">
+      <c r="A168" s="6">
         <v>34</v>
       </c>
-      <c r="B168" s="18" t="s">
+      <c r="B168" s="12" t="s">
         <v>654</v>
       </c>
-      <c r="C168" s="19" t="s">
+      <c r="C168" s="13" t="s">
         <v>655</v>
       </c>
       <c r="D168" s="8" t="s">
@@ -7329,14 +6097,14 @@
         <v>543</v>
       </c>
     </row>
-    <row r="169" spans="1:5" ht="36" x14ac:dyDescent="0.35">
-      <c r="A169" s="20">
+    <row r="169" spans="1:5" ht="37" x14ac:dyDescent="0.45">
+      <c r="A169" s="7">
         <v>72</v>
       </c>
-      <c r="B169" s="21" t="s">
+      <c r="B169" s="14" t="s">
         <v>658</v>
       </c>
-      <c r="C169" s="22" t="s">
+      <c r="C169" s="15" t="s">
         <v>659</v>
       </c>
       <c r="D169" s="9" t="s">
@@ -7346,46 +6114,1169 @@
         <v>543</v>
       </c>
     </row>
-    <row r="170" spans="1:5" ht="36" x14ac:dyDescent="0.35">
-      <c r="A170" s="27">
+    <row r="170" spans="1:5" ht="37" x14ac:dyDescent="0.45">
+      <c r="A170" s="18">
         <v>14</v>
       </c>
-      <c r="B170" s="27" t="s">
+      <c r="B170" s="18" t="s">
         <v>662</v>
       </c>
-      <c r="C170" s="19" t="s">
+      <c r="C170" s="13" t="s">
         <v>663</v>
       </c>
-      <c r="D170" s="28" t="s">
+      <c r="D170" s="18" t="s">
         <v>664</v>
       </c>
-      <c r="E170" s="29"/>
-    </row>
-    <row r="171" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A171" s="27">
+      <c r="E170" s="13"/>
+    </row>
+    <row r="171" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A171" s="18">
         <v>41</v>
       </c>
-      <c r="B171" s="19" t="s">
+      <c r="B171" s="13" t="s">
         <v>665</v>
       </c>
-      <c r="C171" s="19" t="s">
+      <c r="C171" s="13" t="s">
         <v>666</v>
       </c>
-      <c r="D171" s="29"/>
-      <c r="E171" s="29"/>
-    </row>
-    <row r="172" spans="1:5" ht="36" x14ac:dyDescent="0.35">
-      <c r="A172" s="27">
+      <c r="D171" s="13"/>
+      <c r="E171" s="13"/>
+    </row>
+    <row r="172" spans="1:5" ht="37" x14ac:dyDescent="0.45">
+      <c r="A172" s="18">
         <v>72</v>
       </c>
-      <c r="B172" s="27" t="s">
-        <v>671</v>
-      </c>
-      <c r="C172" s="19" t="s">
-        <v>672</v>
-      </c>
-      <c r="D172" s="29"/>
-      <c r="E172" s="29"/>
+      <c r="B172" s="18" t="s">
+        <v>669</v>
+      </c>
+      <c r="C172" s="13" t="s">
+        <v>670</v>
+      </c>
+      <c r="D172" s="13"/>
+      <c r="E172" s="13"/>
+    </row>
+    <row r="173" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A173" s="1">
+        <v>1</v>
+      </c>
+      <c r="B173" t="s">
+        <v>1</v>
+      </c>
+      <c r="C173" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="174" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A174" s="1">
+        <v>2</v>
+      </c>
+      <c r="B174" t="s">
+        <v>3</v>
+      </c>
+      <c r="C174" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="175" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A175" s="1">
+        <v>3</v>
+      </c>
+      <c r="B175" t="s">
+        <v>5</v>
+      </c>
+      <c r="C175" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="176" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A176" s="1">
+        <v>4</v>
+      </c>
+      <c r="B176" t="s">
+        <v>7</v>
+      </c>
+      <c r="C176" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="177" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A177" s="1">
+        <v>5</v>
+      </c>
+      <c r="B177" t="s">
+        <v>9</v>
+      </c>
+      <c r="C177" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="178" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A178" s="1">
+        <v>6</v>
+      </c>
+      <c r="B178" t="s">
+        <v>11</v>
+      </c>
+      <c r="C178" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="179" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A179" s="1">
+        <v>7</v>
+      </c>
+      <c r="B179" t="s">
+        <v>13</v>
+      </c>
+      <c r="C179" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="180" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A180" s="1">
+        <v>8</v>
+      </c>
+      <c r="B180" t="s">
+        <v>15</v>
+      </c>
+      <c r="C180" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="181" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A181" s="1">
+        <v>9</v>
+      </c>
+      <c r="B181" t="s">
+        <v>17</v>
+      </c>
+      <c r="C181" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="182" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A182" s="1">
+        <v>10</v>
+      </c>
+      <c r="B182" t="s">
+        <v>19</v>
+      </c>
+      <c r="C182" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="183" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A183" s="1">
+        <v>11</v>
+      </c>
+      <c r="B183" t="s">
+        <v>241</v>
+      </c>
+      <c r="C183" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="184" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A184" s="1">
+        <v>12</v>
+      </c>
+      <c r="B184" t="s">
+        <v>239</v>
+      </c>
+      <c r="C184" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="185" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A185" s="1">
+        <v>13</v>
+      </c>
+      <c r="B185" t="s">
+        <v>255</v>
+      </c>
+      <c r="C185" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="186" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A186" s="1">
+        <v>14</v>
+      </c>
+      <c r="B186" t="s">
+        <v>21</v>
+      </c>
+      <c r="C186" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="187" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A187" s="1">
+        <v>15</v>
+      </c>
+      <c r="B187" t="s">
+        <v>23</v>
+      </c>
+      <c r="C187" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="188" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A188" s="1">
+        <v>16</v>
+      </c>
+      <c r="B188" t="s">
+        <v>25</v>
+      </c>
+      <c r="C188" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="189" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A189" s="1">
+        <v>17</v>
+      </c>
+      <c r="B189" t="s">
+        <v>27</v>
+      </c>
+      <c r="C189" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="190" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A190" s="1">
+        <v>18</v>
+      </c>
+      <c r="B190" t="s">
+        <v>29</v>
+      </c>
+      <c r="C190" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="191" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A191" s="1">
+        <v>19</v>
+      </c>
+      <c r="B191" t="s">
+        <v>245</v>
+      </c>
+      <c r="C191" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="192" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A192" s="1">
+        <v>20</v>
+      </c>
+      <c r="B192" t="s">
+        <v>243</v>
+      </c>
+      <c r="C192" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="193" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A193" s="1">
+        <v>21</v>
+      </c>
+      <c r="B193" t="s">
+        <v>257</v>
+      </c>
+      <c r="C193" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="194" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A194" s="1">
+        <v>22</v>
+      </c>
+      <c r="B194" t="s">
+        <v>32</v>
+      </c>
+      <c r="C194" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="195" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A195" s="1">
+        <v>23</v>
+      </c>
+      <c r="B195" t="s">
+        <v>34</v>
+      </c>
+      <c r="C195" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="196" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A196" s="1">
+        <v>24</v>
+      </c>
+      <c r="B196" t="s">
+        <v>259</v>
+      </c>
+      <c r="C196" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="197" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A197" s="1">
+        <v>25</v>
+      </c>
+      <c r="B197" t="s">
+        <v>246</v>
+      </c>
+      <c r="C197" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="198" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A198" s="1">
+        <v>26</v>
+      </c>
+      <c r="B198" t="s">
+        <v>36</v>
+      </c>
+      <c r="C198" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="199" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A199" s="1">
+        <v>27</v>
+      </c>
+      <c r="B199" t="s">
+        <v>38</v>
+      </c>
+      <c r="C199" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="200" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A200" s="1">
+        <v>28</v>
+      </c>
+      <c r="B200" t="s">
+        <v>40</v>
+      </c>
+      <c r="C200" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="201" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A201" s="1">
+        <v>29</v>
+      </c>
+      <c r="B201" t="s">
+        <v>42</v>
+      </c>
+      <c r="C201" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="202" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A202" s="1">
+        <v>30</v>
+      </c>
+      <c r="B202" t="s">
+        <v>44</v>
+      </c>
+      <c r="C202" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="203" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A203" s="1">
+        <v>31</v>
+      </c>
+      <c r="B203" t="s">
+        <v>261</v>
+      </c>
+      <c r="C203" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="204" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A204" s="1">
+        <v>32</v>
+      </c>
+      <c r="B204" t="s">
+        <v>46</v>
+      </c>
+      <c r="C204" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="205" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A205" s="1">
+        <v>33</v>
+      </c>
+      <c r="B205" t="s">
+        <v>48</v>
+      </c>
+      <c r="C205" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="206" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A206" s="1">
+        <v>34</v>
+      </c>
+      <c r="B206" t="s">
+        <v>50</v>
+      </c>
+      <c r="C206" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="207" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A207" s="1">
+        <v>35</v>
+      </c>
+      <c r="B207" t="s">
+        <v>52</v>
+      </c>
+      <c r="C207" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="208" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A208" s="1">
+        <v>36</v>
+      </c>
+      <c r="B208" t="s">
+        <v>253</v>
+      </c>
+      <c r="C208" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="209" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A209" s="1">
+        <v>37</v>
+      </c>
+      <c r="B209" t="s">
+        <v>54</v>
+      </c>
+      <c r="C209" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="210" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A210" s="1">
+        <v>38</v>
+      </c>
+      <c r="B210" t="s">
+        <v>56</v>
+      </c>
+      <c r="C210" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="211" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A211" s="1">
+        <v>39</v>
+      </c>
+      <c r="B211" t="s">
+        <v>58</v>
+      </c>
+      <c r="C211" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="212" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A212" s="1">
+        <v>40</v>
+      </c>
+      <c r="B212" t="s">
+        <v>60</v>
+      </c>
+      <c r="C212" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="213" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A213" s="1">
+        <v>41</v>
+      </c>
+      <c r="B213" t="s">
+        <v>62</v>
+      </c>
+      <c r="C213" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="214" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A214" s="1">
+        <v>41</v>
+      </c>
+      <c r="B214" t="s">
+        <v>64</v>
+      </c>
+      <c r="C214" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="215" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A215" s="1">
+        <v>42</v>
+      </c>
+      <c r="B215" t="s">
+        <v>66</v>
+      </c>
+      <c r="C215" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="216" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A216" s="1">
+        <v>43</v>
+      </c>
+      <c r="B216" t="s">
+        <v>68</v>
+      </c>
+      <c r="C216" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="217" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A217" s="1">
+        <v>44</v>
+      </c>
+      <c r="B217" t="s">
+        <v>70</v>
+      </c>
+      <c r="C217" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="218" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A218" s="1">
+        <v>45</v>
+      </c>
+      <c r="B218" t="s">
+        <v>263</v>
+      </c>
+      <c r="C218" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="219" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A219" s="1">
+        <v>46</v>
+      </c>
+      <c r="B219" t="s">
+        <v>265</v>
+      </c>
+      <c r="C219" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="220" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A220" s="1">
+        <v>47</v>
+      </c>
+      <c r="B220" t="s">
+        <v>72</v>
+      </c>
+      <c r="C220" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="221" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A221" s="1">
+        <v>48</v>
+      </c>
+      <c r="B221" t="s">
+        <v>74</v>
+      </c>
+      <c r="C221" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="222" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A222" s="1">
+        <v>49</v>
+      </c>
+      <c r="B222" t="s">
+        <v>76</v>
+      </c>
+      <c r="C222" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="223" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A223" s="1">
+        <v>50</v>
+      </c>
+      <c r="B223" t="s">
+        <v>78</v>
+      </c>
+      <c r="C223" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="224" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A224" s="1">
+        <v>51</v>
+      </c>
+      <c r="B224" t="s">
+        <v>80</v>
+      </c>
+      <c r="C224" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="225" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A225" s="1">
+        <v>52</v>
+      </c>
+      <c r="B225" t="s">
+        <v>235</v>
+      </c>
+      <c r="C225" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="226" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A226" s="1">
+        <v>52</v>
+      </c>
+      <c r="B226" t="s">
+        <v>82</v>
+      </c>
+      <c r="C226" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="227" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A227" s="1">
+        <v>53</v>
+      </c>
+      <c r="B227" t="s">
+        <v>84</v>
+      </c>
+      <c r="C227" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="228" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A228" s="1">
+        <v>53</v>
+      </c>
+      <c r="B228" t="s">
+        <v>86</v>
+      </c>
+      <c r="C228" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="229" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A229" s="1">
+        <v>54</v>
+      </c>
+      <c r="B229" t="s">
+        <v>88</v>
+      </c>
+      <c r="C229" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="230" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A230" s="1">
+        <v>55</v>
+      </c>
+      <c r="B230" t="s">
+        <v>90</v>
+      </c>
+      <c r="C230" t="s">
+        <v>91</v>
+      </c>
+      <c r="E230" s="20"/>
+    </row>
+    <row r="231" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A231" s="1">
+        <v>56</v>
+      </c>
+      <c r="B231" t="s">
+        <v>92</v>
+      </c>
+      <c r="C231" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="232" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A232" s="1">
+        <v>57</v>
+      </c>
+      <c r="B232" t="s">
+        <v>94</v>
+      </c>
+      <c r="C232" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="233" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A233" s="1">
+        <v>58</v>
+      </c>
+      <c r="B233" t="s">
+        <v>96</v>
+      </c>
+      <c r="C233" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="234" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A234" s="1">
+        <v>59</v>
+      </c>
+      <c r="B234" t="s">
+        <v>98</v>
+      </c>
+      <c r="C234" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="235" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A235" s="1">
+        <v>60</v>
+      </c>
+      <c r="B235" t="s">
+        <v>100</v>
+      </c>
+      <c r="C235" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="236" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A236" s="1">
+        <v>61</v>
+      </c>
+      <c r="B236" t="s">
+        <v>102</v>
+      </c>
+      <c r="C236" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="237" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A237" s="1">
+        <v>62</v>
+      </c>
+      <c r="B237" t="s">
+        <v>104</v>
+      </c>
+      <c r="C237" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="238" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A238" s="1">
+        <v>63</v>
+      </c>
+      <c r="B238" t="s">
+        <v>106</v>
+      </c>
+      <c r="C238" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="239" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A239" s="1">
+        <v>64</v>
+      </c>
+      <c r="B239" t="s">
+        <v>108</v>
+      </c>
+      <c r="C239" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="240" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A240" s="1">
+        <v>65</v>
+      </c>
+      <c r="B240" t="s">
+        <v>110</v>
+      </c>
+      <c r="C240" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="241" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A241" s="1">
+        <v>66</v>
+      </c>
+      <c r="B241" t="s">
+        <v>112</v>
+      </c>
+      <c r="C241" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="242" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A242" s="1">
+        <v>67</v>
+      </c>
+      <c r="B242" t="s">
+        <v>267</v>
+      </c>
+      <c r="C242" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="243" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A243" s="1">
+        <v>68</v>
+      </c>
+      <c r="B243" t="s">
+        <v>114</v>
+      </c>
+      <c r="C243" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="244" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A244" s="1">
+        <v>69</v>
+      </c>
+      <c r="B244" t="s">
+        <v>116</v>
+      </c>
+      <c r="C244" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="245" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A245" s="1">
+        <v>70</v>
+      </c>
+      <c r="B245" t="s">
+        <v>118</v>
+      </c>
+      <c r="C245" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="246" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A246" s="1">
+        <v>71</v>
+      </c>
+      <c r="B246" t="s">
+        <v>120</v>
+      </c>
+      <c r="C246" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="247" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A247" s="1">
+        <v>72</v>
+      </c>
+      <c r="B247" t="s">
+        <v>122</v>
+      </c>
+      <c r="C247" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="248" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A248" s="1">
+        <v>73</v>
+      </c>
+      <c r="B248" t="s">
+        <v>124</v>
+      </c>
+      <c r="C248" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="249" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A249" s="1">
+        <v>74</v>
+      </c>
+      <c r="B249" t="s">
+        <v>126</v>
+      </c>
+      <c r="C249" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="250" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A250" s="1">
+        <v>75</v>
+      </c>
+      <c r="B250" t="s">
+        <v>128</v>
+      </c>
+      <c r="C250" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="251" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A251" s="1">
+        <v>76</v>
+      </c>
+      <c r="B251" t="s">
+        <v>130</v>
+      </c>
+      <c r="C251" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="252" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A252" s="1">
+        <v>77</v>
+      </c>
+      <c r="B252" t="s">
+        <v>132</v>
+      </c>
+      <c r="C252" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="253" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A253" s="1">
+        <v>78</v>
+      </c>
+      <c r="B253" t="s">
+        <v>134</v>
+      </c>
+      <c r="C253" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="254" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A254" s="1">
+        <v>79</v>
+      </c>
+      <c r="B254" t="s">
+        <v>136</v>
+      </c>
+      <c r="C254" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="255" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A255" s="1">
+        <v>80</v>
+      </c>
+      <c r="B255" t="s">
+        <v>138</v>
+      </c>
+      <c r="C255" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="256" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A256" s="1">
+        <v>81</v>
+      </c>
+      <c r="B256" t="s">
+        <v>140</v>
+      </c>
+      <c r="C256" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="257" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A257" s="1">
+        <v>82</v>
+      </c>
+      <c r="B257" t="s">
+        <v>249</v>
+      </c>
+      <c r="C257" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="258" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A258" s="1">
+        <v>83</v>
+      </c>
+      <c r="B258" t="s">
+        <v>142</v>
+      </c>
+      <c r="C258" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="259" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A259" s="1">
+        <v>84</v>
+      </c>
+      <c r="B259" t="s">
+        <v>144</v>
+      </c>
+      <c r="C259" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="260" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A260" s="1">
+        <v>85</v>
+      </c>
+      <c r="B260" t="s">
+        <v>146</v>
+      </c>
+      <c r="C260" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="261" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A261" s="1">
+        <v>86</v>
+      </c>
+      <c r="B261" t="s">
+        <v>148</v>
+      </c>
+      <c r="C261" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="262" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A262" s="1">
+        <v>87</v>
+      </c>
+      <c r="B262" t="s">
+        <v>150</v>
+      </c>
+      <c r="C262" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="263" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A263" s="1">
+        <v>88</v>
+      </c>
+      <c r="B263" t="s">
+        <v>152</v>
+      </c>
+      <c r="C263" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="264" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A264" s="1">
+        <v>89</v>
+      </c>
+      <c r="B264" t="s">
+        <v>154</v>
+      </c>
+      <c r="C264" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="265" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A265" s="1">
+        <v>90</v>
+      </c>
+      <c r="B265" t="s">
+        <v>251</v>
+      </c>
+      <c r="C265" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="266" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A266" s="1">
+        <v>91</v>
+      </c>
+      <c r="B266" t="s">
+        <v>156</v>
+      </c>
+      <c r="C266" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="267" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A267" s="1">
+        <v>92</v>
+      </c>
+      <c r="B267" t="s">
+        <v>158</v>
+      </c>
+      <c r="C267" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="268" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A268" s="1">
+        <v>93</v>
+      </c>
+      <c r="B268" t="s">
+        <v>159</v>
+      </c>
+      <c r="C268" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="269" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A269" s="1">
+        <v>94</v>
+      </c>
+      <c r="B269" t="s">
+        <v>161</v>
+      </c>
+      <c r="C269" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="270" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A270" s="1">
+        <v>95</v>
+      </c>
+      <c r="B270" t="s">
+        <v>163</v>
+      </c>
+      <c r="C270" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="271" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A271" s="1">
+        <v>96</v>
+      </c>
+      <c r="B271" t="s">
+        <v>165</v>
+      </c>
+      <c r="C271" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="272" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A272" s="1">
+        <v>97</v>
+      </c>
+      <c r="B272" t="s">
+        <v>167</v>
+      </c>
+      <c r="C272" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="273" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A273" s="1">
+        <v>98</v>
+      </c>
+      <c r="B273" t="s">
+        <v>169</v>
+      </c>
+      <c r="C273" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="274" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A274" s="1">
+        <v>99</v>
+      </c>
+      <c r="B274" t="s">
+        <v>171</v>
+      </c>
+      <c r="C274" t="s">
+        <v>172</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -7399,357 +7290,357 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{746A171E-0909-4EAC-9BA8-30B6C7D88F06}">
   <dimension ref="A1:H32"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="18" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="10.85546875" defaultRowHeight="18.5" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A1" s="4" t="s">
-        <v>677</v>
-      </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
+        <v>675</v>
+      </c>
+      <c r="B1" s="3"/>
+      <c r="C1" s="3"/>
       <c r="D1" s="3"/>
       <c r="E1" s="3"/>
       <c r="F1" s="3"/>
       <c r="G1" s="3"/>
       <c r="H1" s="3"/>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A2" s="11" t="s">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A2" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="B2" s="12" t="s">
+      <c r="B2" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="12"/>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A3" s="11">
+      <c r="C2" s="19"/>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A3" s="1">
         <v>2</v>
       </c>
-      <c r="B3" s="13" t="s">
+      <c r="B3" t="s">
         <v>175</v>
       </c>
-      <c r="C3" s="14" t="s">
+      <c r="C3" s="10" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A4" s="11">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A4" s="1">
         <v>3</v>
       </c>
-      <c r="B4" s="13" t="s">
+      <c r="B4" t="s">
         <v>237</v>
       </c>
-      <c r="C4" s="14" t="s">
+      <c r="C4" s="10" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A5" s="11">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A5" s="1">
         <v>4</v>
       </c>
-      <c r="B5" s="13" t="s">
+      <c r="B5" t="s">
         <v>176</v>
       </c>
-      <c r="C5" s="14" t="s">
+      <c r="C5" s="10" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A6" s="11">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A6" s="1">
         <v>4</v>
       </c>
-      <c r="B6" s="13" t="s">
+      <c r="B6" t="s">
         <v>185</v>
       </c>
-      <c r="C6" s="14" t="s">
+      <c r="C6" s="10" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A7" s="11">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A7" s="1">
         <v>5</v>
       </c>
-      <c r="B7" s="13" t="s">
+      <c r="B7" t="s">
         <v>230</v>
       </c>
-      <c r="C7" s="13" t="s">
+      <c r="C7" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A8" s="11">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A8" s="1">
         <v>10</v>
       </c>
-      <c r="B8" s="13" t="s">
+      <c r="B8" t="s">
         <v>179</v>
       </c>
-      <c r="C8" s="13" t="s">
+      <c r="C8" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A9" s="11">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A9" s="1">
         <v>26</v>
       </c>
-      <c r="B9" s="13" t="s">
+      <c r="B9" t="s">
         <v>181</v>
       </c>
-      <c r="C9" s="13" t="s">
+      <c r="C9" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A10" s="11">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A10" s="1">
         <v>2</v>
       </c>
-      <c r="B10" s="13" t="s">
+      <c r="B10" t="s">
         <v>183</v>
       </c>
-      <c r="C10" s="13" t="s">
+      <c r="C10" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A11" s="11" t="s">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A11" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="B11" s="13" t="s">
+      <c r="B11" t="s">
         <v>187</v>
       </c>
-      <c r="C11" s="13" t="s">
+      <c r="C11" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A12" s="11" t="s">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A12" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="B12" s="13" t="s">
+      <c r="B12" t="s">
         <v>189</v>
       </c>
-      <c r="C12" s="13" t="s">
+      <c r="C12" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A13" s="11">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A13" s="1">
         <v>24</v>
       </c>
-      <c r="B13" s="13" t="s">
+      <c r="B13" t="s">
         <v>225</v>
       </c>
-      <c r="C13" s="13" t="s">
+      <c r="C13" t="s">
         <v>226</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A14" s="11">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A14" s="1">
         <v>44</v>
       </c>
-      <c r="B14" s="13" t="s">
+      <c r="B14" t="s">
         <v>223</v>
       </c>
-      <c r="C14" s="13" t="s">
+      <c r="C14" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A15" s="11">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A15" s="1">
         <v>13</v>
       </c>
-      <c r="B15" s="13" t="s">
+      <c r="B15" t="s">
         <v>221</v>
       </c>
-      <c r="C15" s="13" t="s">
+      <c r="C15" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A16" s="11">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A16" s="1">
         <v>27</v>
       </c>
-      <c r="B16" s="13" t="s">
+      <c r="B16" t="s">
         <v>219</v>
       </c>
-      <c r="C16" s="13" t="s">
+      <c r="C16" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A17" s="11">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A17" s="1">
         <v>23</v>
       </c>
-      <c r="B17" s="13" t="s">
+      <c r="B17" t="s">
         <v>217</v>
       </c>
-      <c r="C17" s="13" t="s">
+      <c r="C17" t="s">
         <v>218</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A18" s="11">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A18" s="1">
         <v>54</v>
       </c>
-      <c r="B18" s="13" t="s">
+      <c r="B18" t="s">
         <v>215</v>
       </c>
-      <c r="C18" s="13" t="s">
+      <c r="C18" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A19" s="11">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A19" s="1">
         <v>55</v>
       </c>
-      <c r="B19" s="13" t="s">
+      <c r="B19" t="s">
         <v>213</v>
       </c>
-      <c r="C19" s="13" t="s">
+      <c r="C19" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A20" s="11">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A20" s="1">
         <v>57</v>
       </c>
-      <c r="B20" s="13" t="s">
+      <c r="B20" t="s">
         <v>211</v>
       </c>
-      <c r="C20" s="13" t="s">
+      <c r="C20" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A21" s="11">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A21" s="1">
         <v>56</v>
       </c>
-      <c r="B21" s="13" t="s">
+      <c r="B21" t="s">
         <v>209</v>
       </c>
-      <c r="C21" s="13" t="s">
+      <c r="C21" t="s">
         <v>210</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A22" s="11">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A22" s="1">
         <v>45</v>
       </c>
-      <c r="B22" s="13" t="s">
+      <c r="B22" t="s">
         <v>207</v>
       </c>
-      <c r="C22" s="13" t="s">
+      <c r="C22" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A23" s="11">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A23" s="1">
         <v>40</v>
       </c>
-      <c r="B23" s="13" t="s">
+      <c r="B23" t="s">
         <v>205</v>
       </c>
-      <c r="C23" s="13" t="s">
+      <c r="C23" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A24" s="11">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A24" s="1">
         <v>41</v>
       </c>
-      <c r="B24" s="13" t="s">
+      <c r="B24" t="s">
         <v>204</v>
       </c>
-      <c r="C24" s="13" t="s">
+      <c r="C24" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A25" s="11">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A25" s="1">
         <v>95</v>
       </c>
-      <c r="B25" s="13" t="s">
+      <c r="B25" t="s">
         <v>201</v>
       </c>
-      <c r="C25" s="13" t="s">
+      <c r="C25" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A26" s="11">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A26" s="1">
         <v>6</v>
       </c>
-      <c r="B26" s="13" t="s">
+      <c r="B26" t="s">
         <v>199</v>
       </c>
-      <c r="C26" s="13" t="s">
+      <c r="C26" t="s">
         <v>200</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A27" s="11">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A27" s="1">
         <v>5</v>
       </c>
-      <c r="B27" s="13" t="s">
+      <c r="B27" t="s">
         <v>197</v>
       </c>
-      <c r="C27" s="13" t="s">
+      <c r="C27" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A28" s="11">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A28" s="1">
         <v>3</v>
       </c>
-      <c r="B28" s="13" t="s">
+      <c r="B28" t="s">
         <v>195</v>
       </c>
-      <c r="C28" s="13" t="s">
+      <c r="C28" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A29" s="11">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A29" s="1">
         <v>2</v>
       </c>
-      <c r="B29" s="13" t="s">
+      <c r="B29" t="s">
         <v>193</v>
       </c>
-      <c r="C29" s="13" t="s">
+      <c r="C29" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A30" s="11">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A30" s="1">
         <v>1</v>
       </c>
-      <c r="B30" s="13" t="s">
+      <c r="B30" t="s">
         <v>191</v>
       </c>
-      <c r="C30" s="14" t="s">
+      <c r="C30" s="10" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A31" s="11">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A31" s="1">
         <v>87</v>
       </c>
-      <c r="B31" s="13" t="s">
+      <c r="B31" t="s">
         <v>231</v>
       </c>
-      <c r="C31" s="13" t="s">
+      <c r="C31" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A32" s="11">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A32" s="1">
         <v>4</v>
       </c>
-      <c r="B32" s="13" t="s">
-        <v>675</v>
-      </c>
-      <c r="C32" s="13" t="s">
-        <v>676</v>
+      <c r="B32" t="s">
+        <v>673</v>
+      </c>
+      <c r="C32" t="s">
+        <v>674</v>
       </c>
     </row>
   </sheetData>
@@ -7763,10 +7654,10 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B49A6C1-9319-47F6-B53F-AD173F9BA821}">
-  <dimension ref="A1:H23"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="18" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:F23"/>
+  <sheetFormatPr defaultColWidth="10.85546875" defaultRowHeight="18.5" x14ac:dyDescent="0.45"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A1" s="4" t="s">
         <v>227</v>
       </c>
@@ -7776,23 +7667,23 @@
       <c r="E1" s="3"/>
       <c r="F1" s="3"/>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A2" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="B2" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="10"/>
-    </row>
-    <row r="3" spans="1:6" ht="36" x14ac:dyDescent="0.35">
-      <c r="A3" s="17">
+      <c r="C2" s="19"/>
+    </row>
+    <row r="3" spans="1:6" ht="37" x14ac:dyDescent="0.45">
+      <c r="A3" s="6">
         <v>8</v>
       </c>
-      <c r="B3" s="18" t="s">
+      <c r="B3" s="12" t="s">
         <v>618</v>
       </c>
-      <c r="C3" s="19" t="s">
+      <c r="C3" s="13" t="s">
         <v>619</v>
       </c>
       <c r="D3" s="8" t="s">
@@ -7802,14 +7693,14 @@
         <v>543</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="36" x14ac:dyDescent="0.35">
-      <c r="A4" s="17">
+    <row r="4" spans="1:6" ht="37" x14ac:dyDescent="0.45">
+      <c r="A4" s="6">
         <v>9</v>
       </c>
-      <c r="B4" s="18" t="s">
+      <c r="B4" s="12" t="s">
         <v>624</v>
       </c>
-      <c r="C4" s="19" t="s">
+      <c r="C4" s="13" t="s">
         <v>625</v>
       </c>
       <c r="D4" s="8" t="s">
@@ -7819,14 +7710,14 @@
         <v>543</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="36" x14ac:dyDescent="0.35">
-      <c r="A5" s="17">
+    <row r="5" spans="1:6" ht="37" x14ac:dyDescent="0.45">
+      <c r="A5" s="6">
         <v>10</v>
       </c>
-      <c r="B5" s="18" t="s">
+      <c r="B5" s="12" t="s">
         <v>626</v>
       </c>
-      <c r="C5" s="19" t="s">
+      <c r="C5" s="13" t="s">
         <v>627</v>
       </c>
       <c r="D5" s="8" t="s">
@@ -7836,14 +7727,14 @@
         <v>543</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="36" x14ac:dyDescent="0.35">
-      <c r="A6" s="17">
+    <row r="6" spans="1:6" ht="37" x14ac:dyDescent="0.45">
+      <c r="A6" s="6">
         <v>11</v>
       </c>
-      <c r="B6" s="18" t="s">
+      <c r="B6" s="12" t="s">
         <v>628</v>
       </c>
-      <c r="C6" s="19" t="s">
+      <c r="C6" s="13" t="s">
         <v>629</v>
       </c>
       <c r="D6" s="8" t="s">
@@ -7853,14 +7744,14 @@
         <v>543</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="36" x14ac:dyDescent="0.35">
-      <c r="A7" s="17">
+    <row r="7" spans="1:6" ht="37" x14ac:dyDescent="0.45">
+      <c r="A7" s="6">
         <v>12</v>
       </c>
-      <c r="B7" s="18" t="s">
+      <c r="B7" s="12" t="s">
         <v>614</v>
       </c>
-      <c r="C7" s="19" t="s">
+      <c r="C7" s="13" t="s">
         <v>615</v>
       </c>
       <c r="D7" s="8" t="s">
@@ -7870,14 +7761,14 @@
         <v>543</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="36" x14ac:dyDescent="0.35">
-      <c r="A8" s="17">
+    <row r="8" spans="1:6" ht="37" x14ac:dyDescent="0.45">
+      <c r="A8" s="6">
         <v>13</v>
       </c>
-      <c r="B8" s="18" t="s">
+      <c r="B8" s="12" t="s">
         <v>622</v>
       </c>
-      <c r="C8" s="19" t="s">
+      <c r="C8" s="13" t="s">
         <v>623</v>
       </c>
       <c r="D8" s="8" t="s">
@@ -7887,14 +7778,14 @@
         <v>543</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="36" x14ac:dyDescent="0.35">
-      <c r="A9" s="17">
+    <row r="9" spans="1:6" ht="37" x14ac:dyDescent="0.45">
+      <c r="A9" s="6">
         <v>14</v>
       </c>
-      <c r="B9" s="18" t="s">
+      <c r="B9" s="12" t="s">
         <v>656</v>
       </c>
-      <c r="C9" s="19" t="s">
+      <c r="C9" s="13" t="s">
         <v>657</v>
       </c>
       <c r="D9" s="8" t="s">
@@ -7904,14 +7795,14 @@
         <v>543</v>
       </c>
     </row>
-    <row r="10" spans="1:6" ht="36" x14ac:dyDescent="0.35">
-      <c r="A10" s="17">
+    <row r="10" spans="1:6" ht="37" x14ac:dyDescent="0.45">
+      <c r="A10" s="6">
         <v>15</v>
       </c>
-      <c r="B10" s="18" t="s">
+      <c r="B10" s="12" t="s">
         <v>591</v>
       </c>
-      <c r="C10" s="19" t="s">
+      <c r="C10" s="13" t="s">
         <v>592</v>
       </c>
       <c r="D10" s="8" t="s">
@@ -7921,14 +7812,14 @@
         <v>543</v>
       </c>
     </row>
-    <row r="11" spans="1:6" ht="36" x14ac:dyDescent="0.35">
-      <c r="A11" s="17">
+    <row r="11" spans="1:6" ht="37" x14ac:dyDescent="0.45">
+      <c r="A11" s="6">
         <v>16</v>
       </c>
-      <c r="B11" s="18" t="s">
+      <c r="B11" s="12" t="s">
         <v>630</v>
       </c>
-      <c r="C11" s="19" t="s">
+      <c r="C11" s="13" t="s">
         <v>631</v>
       </c>
       <c r="D11" s="8" t="s">
@@ -7938,14 +7829,14 @@
         <v>543</v>
       </c>
     </row>
-    <row r="12" spans="1:6" ht="36" x14ac:dyDescent="0.35">
-      <c r="A12" s="17">
+    <row r="12" spans="1:6" ht="37" x14ac:dyDescent="0.45">
+      <c r="A12" s="6">
         <v>17</v>
       </c>
-      <c r="B12" s="18" t="s">
+      <c r="B12" s="12" t="s">
         <v>612</v>
       </c>
-      <c r="C12" s="19" t="s">
+      <c r="C12" s="13" t="s">
         <v>613</v>
       </c>
       <c r="D12" s="8" t="s">
@@ -7955,14 +7846,14 @@
         <v>543</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="36" x14ac:dyDescent="0.35">
-      <c r="A13" s="17">
+    <row r="13" spans="1:6" ht="37" x14ac:dyDescent="0.45">
+      <c r="A13" s="6">
         <v>26</v>
       </c>
-      <c r="B13" s="18" t="s">
+      <c r="B13" s="12" t="s">
         <v>570</v>
       </c>
-      <c r="C13" s="19" t="s">
+      <c r="C13" s="13" t="s">
         <v>571</v>
       </c>
       <c r="D13" s="8" t="s">
@@ -7972,14 +7863,14 @@
         <v>543</v>
       </c>
     </row>
-    <row r="14" spans="1:6" ht="36" x14ac:dyDescent="0.35">
-      <c r="A14" s="17">
+    <row r="14" spans="1:6" ht="37" x14ac:dyDescent="0.45">
+      <c r="A14" s="6">
         <v>27</v>
       </c>
-      <c r="B14" s="18" t="s">
+      <c r="B14" s="12" t="s">
         <v>573</v>
       </c>
-      <c r="C14" s="19" t="s">
+      <c r="C14" s="13" t="s">
         <v>572</v>
       </c>
       <c r="D14" s="8" t="s">
@@ -7989,14 +7880,14 @@
         <v>543</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="36" x14ac:dyDescent="0.35">
-      <c r="A15" s="17">
+    <row r="15" spans="1:6" ht="37" x14ac:dyDescent="0.45">
+      <c r="A15" s="6">
         <v>28</v>
       </c>
-      <c r="B15" s="18" t="s">
+      <c r="B15" s="12" t="s">
         <v>574</v>
       </c>
-      <c r="C15" s="19" t="s">
+      <c r="C15" s="13" t="s">
         <v>567</v>
       </c>
       <c r="D15" s="8" t="s">
@@ -8006,14 +7897,14 @@
         <v>543</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="36" x14ac:dyDescent="0.35">
-      <c r="A16" s="17">
+    <row r="16" spans="1:6" ht="37" x14ac:dyDescent="0.45">
+      <c r="A16" s="6">
         <v>29</v>
       </c>
-      <c r="B16" s="18" t="s">
+      <c r="B16" s="12" t="s">
         <v>566</v>
       </c>
-      <c r="C16" s="19" t="s">
+      <c r="C16" s="13" t="s">
         <v>567</v>
       </c>
       <c r="D16" s="8" t="s">
@@ -8023,14 +7914,14 @@
         <v>543</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="36" x14ac:dyDescent="0.35">
-      <c r="A17" s="17">
+    <row r="17" spans="1:5" ht="37" x14ac:dyDescent="0.45">
+      <c r="A17" s="6">
         <v>30</v>
       </c>
-      <c r="B17" s="18" t="s">
+      <c r="B17" s="12" t="s">
         <v>568</v>
       </c>
-      <c r="C17" s="19" t="s">
+      <c r="C17" s="13" t="s">
         <v>569</v>
       </c>
       <c r="D17" s="8" t="s">
@@ -8040,14 +7931,14 @@
         <v>543</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="36" x14ac:dyDescent="0.35">
-      <c r="A18" s="17">
+    <row r="18" spans="1:5" ht="37" x14ac:dyDescent="0.45">
+      <c r="A18" s="6">
         <v>69</v>
       </c>
-      <c r="B18" s="18" t="s">
+      <c r="B18" s="12" t="s">
         <v>585</v>
       </c>
-      <c r="C18" s="19" t="s">
+      <c r="C18" s="13" t="s">
         <v>586</v>
       </c>
       <c r="D18" s="8" t="s">
@@ -8057,14 +7948,14 @@
         <v>543</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="36" x14ac:dyDescent="0.35">
-      <c r="A19" s="17">
+    <row r="19" spans="1:5" ht="37" x14ac:dyDescent="0.45">
+      <c r="A19" s="6">
         <v>77</v>
       </c>
-      <c r="B19" s="18" t="s">
+      <c r="B19" s="12" t="s">
         <v>616</v>
       </c>
-      <c r="C19" s="19" t="s">
+      <c r="C19" s="13" t="s">
         <v>617</v>
       </c>
       <c r="D19" s="8" t="s">
@@ -8074,14 +7965,14 @@
         <v>543</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="36" x14ac:dyDescent="0.35">
-      <c r="A20" s="17">
+    <row r="20" spans="1:5" ht="37" x14ac:dyDescent="0.45">
+      <c r="A20" s="6">
         <v>78</v>
       </c>
-      <c r="B20" s="18" t="s">
+      <c r="B20" s="12" t="s">
         <v>620</v>
       </c>
-      <c r="C20" s="19" t="s">
+      <c r="C20" s="13" t="s">
         <v>621</v>
       </c>
       <c r="D20" s="8" t="s">
@@ -8091,14 +7982,14 @@
         <v>543</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="36" x14ac:dyDescent="0.35">
-      <c r="A21" s="17">
+    <row r="21" spans="1:5" ht="37" x14ac:dyDescent="0.45">
+      <c r="A21" s="6">
         <v>79</v>
       </c>
-      <c r="B21" s="18" t="s">
+      <c r="B21" s="12" t="s">
         <v>583</v>
       </c>
-      <c r="C21" s="19" t="s">
+      <c r="C21" s="13" t="s">
         <v>584</v>
       </c>
       <c r="D21" s="8" t="s">
@@ -8108,14 +7999,14 @@
         <v>543</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="36" x14ac:dyDescent="0.35">
-      <c r="A22" s="20">
+    <row r="22" spans="1:5" ht="37" x14ac:dyDescent="0.45">
+      <c r="A22" s="7">
         <v>80</v>
       </c>
-      <c r="B22" s="21" t="s">
+      <c r="B22" s="14" t="s">
         <v>660</v>
       </c>
-      <c r="C22" s="22" t="s">
+      <c r="C22" s="15" t="s">
         <v>661</v>
       </c>
       <c r="D22" s="9" t="s">
@@ -8125,21 +8016,18 @@
         <v>543</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A23" s="23">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A23" s="16">
         <v>19</v>
       </c>
-      <c r="B23" s="24" t="s">
+      <c r="B23" s="13" t="s">
         <v>228</v>
       </c>
-      <c r="C23" s="24" t="s">
+      <c r="C23" s="13" t="s">
         <v>229</v>
       </c>
-      <c r="D23" s="16"/>
-      <c r="E23" s="16"/>
-      <c r="F23" s="15"/>
-      <c r="G23" s="15"/>
-      <c r="H23" s="15"/>
+      <c r="D23" s="11"/>
+      <c r="E23" s="11"/>
     </row>
   </sheetData>
   <autoFilter ref="A2:C21" xr:uid="{0B49A6C1-9319-47F6-B53F-AD173F9BA821}">
@@ -8157,6 +8045,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="bcc43101-2024-4ab1-a533-f1debe28b476" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="a1b2e515-18f6-41bb-93d3-ae289a4d5f75">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x010100D4FB81B1B318F948BEC23BF7923B58F6" ma:contentTypeVersion="19" ma:contentTypeDescription="Ein neues Dokument erstellen." ma:contentTypeScope="" ma:versionID="7e84b9e5ca734c0933fbad4057cd2750">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="bcc43101-2024-4ab1-a533-f1debe28b476" xmlns:ns3="a1b2e515-18f6-41bb-93d3-ae289a4d5f75" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="2cbde481a808845b64c50f1e216eef3e" ns2:_="" ns3:_="">
     <xsd:import namespace="bcc43101-2024-4ab1-a533-f1debe28b476"/>
@@ -8411,27 +8319,26 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="bcc43101-2024-4ab1-a533-f1debe28b476" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="a1b2e515-18f6-41bb-93d3-ae289a4d5f75">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AB3C916F-3A2F-4E38-B49A-9D1E5A7BCD42}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1BB1FB75-2D86-4574-8CCD-ACA07892C7C5}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="bcc43101-2024-4ab1-a533-f1debe28b476"/>
+    <ds:schemaRef ds:uri="a1b2e515-18f6-41bb-93d3-ae289a4d5f75"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AAFFD87C-395B-4A06-811F-660D7A978ECE}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -8448,23 +8355,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1BB1FB75-2D86-4574-8CCD-ACA07892C7C5}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="bcc43101-2024-4ab1-a533-f1debe28b476"/>
-    <ds:schemaRef ds:uri="a1b2e515-18f6-41bb-93d3-ae289a4d5f75"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AB3C916F-3A2F-4E38-B49A-9D1E5A7BCD42}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>